--- a/clustering/sepsectors/mining sector (factoriescap_s) 0.xlsx
+++ b/clustering/sepsectors/mining sector (factoriescap_s) 0.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="27">
   <si>
     <t>sector</t>
   </si>
@@ -91,6 +91,15 @@
   </si>
   <si>
     <t xml:space="preserve">Доли сквозных техн. и обучения персонала получены от ITcosts_s </t>
+  </si>
+  <si>
+    <t>верхний кластер:</t>
+  </si>
+  <si>
+    <t>нижний кластер:</t>
+  </si>
+  <si>
+    <t>разница</t>
   </si>
 </sst>
 </file>
@@ -100,7 +109,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.000%"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -112,6 +121,8 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
     </font>
     <font>
       <sz val="11"/>
@@ -123,6 +134,15 @@
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="204"/>
@@ -165,7 +185,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -180,6 +200,10 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -483,7 +507,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J23"/>
+  <dimension ref="A1:J55"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="67" customWidth="1"/>
@@ -974,11 +998,764 @@
         <v>1.0604112949224313E-3</v>
       </c>
     </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A26" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C26" s="2">
+        <v>2022</v>
+      </c>
+      <c r="D26" s="6">
+        <v>12596210.486</v>
+      </c>
+      <c r="E26" s="6">
+        <v>29618.176784399999</v>
+      </c>
+      <c r="F26" s="3">
+        <v>1.244197192428451E-3</v>
+      </c>
+      <c r="G26" s="3">
+        <v>9.1204876912707078E-4</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A27" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C27" s="2">
+        <v>2021</v>
+      </c>
+      <c r="D27" s="6">
+        <v>12460128.155999999</v>
+      </c>
+      <c r="E27" s="6">
+        <v>32672.95173072</v>
+      </c>
+      <c r="F27" s="3">
+        <v>2.8388815641284579E-2</v>
+      </c>
+      <c r="G27" s="3">
+        <v>1.009990774998547E-3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A28" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C28" s="2">
+        <v>2023</v>
+      </c>
+      <c r="D28" s="6">
+        <v>11423484.0792</v>
+      </c>
+      <c r="E28" s="6">
+        <v>30582.725913679998</v>
+      </c>
+      <c r="F28" s="3">
+        <v>8.6595807302297054E-5</v>
+      </c>
+      <c r="G28" s="3">
+        <v>1.69804857508698E-3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A29" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C29" s="2">
+        <v>2024</v>
+      </c>
+      <c r="D29" s="6">
+        <v>11300772.48</v>
+      </c>
+      <c r="E29" s="6">
+        <v>31974.339456000002</v>
+      </c>
+      <c r="F29" s="3">
+        <v>5.7574468505698965E-4</v>
+      </c>
+      <c r="G29" s="3">
+        <v>6.8807976565944413E-4</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B31" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="D31" s="6">
+        <f>AVERAGE(D26:D27)</f>
+        <v>12528169.320999999</v>
+      </c>
+      <c r="E31" s="6">
+        <f t="shared" ref="E31:G31" si="2">AVERAGE(E26:E27)</f>
+        <v>31145.56425756</v>
+      </c>
+      <c r="F31" s="3">
+        <f t="shared" si="2"/>
+        <v>1.4816506416856515E-2</v>
+      </c>
+      <c r="G31" s="3">
+        <f t="shared" si="2"/>
+        <v>9.6101977206280889E-4</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B32" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="D32" s="6">
+        <f>AVERAGE(D28:D29)</f>
+        <v>11362128.2796</v>
+      </c>
+      <c r="E32" s="6">
+        <f t="shared" ref="E32:G32" si="3">AVERAGE(E28:E29)</f>
+        <v>31278.53268484</v>
+      </c>
+      <c r="F32" s="3">
+        <f t="shared" si="3"/>
+        <v>3.3117024617964334E-4</v>
+      </c>
+      <c r="G32" s="3">
+        <f t="shared" si="3"/>
+        <v>1.193064170373212E-3</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B34" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D34" s="6">
+        <f>D31/D32</f>
+        <v>1.1026252311808127</v>
+      </c>
+      <c r="E34" s="6">
+        <f t="shared" ref="E34:G34" si="4">E31/E32</f>
+        <v>0.99574889178403025</v>
+      </c>
+      <c r="F34" s="6">
+        <f t="shared" si="4"/>
+        <v>44.739847820807242</v>
+      </c>
+      <c r="G34" s="6">
+        <f t="shared" si="4"/>
+        <v>0.8055055175801521</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A37" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C37" s="2">
+        <v>2021</v>
+      </c>
+      <c r="D37" s="6">
+        <v>1743254.7426</v>
+      </c>
+      <c r="E37" s="6">
+        <v>5649.2667995399997</v>
+      </c>
+      <c r="F37" s="3">
+        <v>4.3069526144492228E-2</v>
+      </c>
+      <c r="G37" s="3">
+        <v>2.415866866318173E-3</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A38" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C38" s="2">
+        <v>2023</v>
+      </c>
+      <c r="D38" s="6">
+        <v>1196714.5288</v>
+      </c>
+      <c r="E38" s="6">
+        <v>5296.7583626400001</v>
+      </c>
+      <c r="F38" s="3">
+        <v>0.1023070329623097</v>
+      </c>
+      <c r="G38" s="3">
+        <v>6.5499992306063972E-4</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A39" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C39" s="2">
+        <v>2024</v>
+      </c>
+      <c r="D39" s="6">
+        <v>1186586.3999999999</v>
+      </c>
+      <c r="E39" s="6">
+        <v>4305.8265600000004</v>
+      </c>
+      <c r="F39" s="3">
+        <v>7.4943726483957598E-2</v>
+      </c>
+      <c r="G39" s="3">
+        <v>1.251650972211942E-3</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A40" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C40" s="2">
+        <v>2022</v>
+      </c>
+      <c r="D40" s="6">
+        <v>1110225.9291999999</v>
+      </c>
+      <c r="E40" s="6">
+        <v>5731.3955529599998</v>
+      </c>
+      <c r="F40" s="3">
+        <v>2.961302102283718E-2</v>
+      </c>
+      <c r="G40" s="3">
+        <v>1.1157895805494109E-3</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B42" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="D42" s="6">
+        <f>AVERAGE(D37:D38)</f>
+        <v>1469984.6357</v>
+      </c>
+      <c r="E42" s="6">
+        <f t="shared" ref="E42:G42" si="5">AVERAGE(E37:E38)</f>
+        <v>5473.0125810899999</v>
+      </c>
+      <c r="F42" s="3">
+        <f t="shared" si="5"/>
+        <v>7.2688279553400958E-2</v>
+      </c>
+      <c r="G42" s="3">
+        <f t="shared" si="5"/>
+        <v>1.5354333946894063E-3</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B43" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="D43" s="6">
+        <f>AVERAGE(D39:D40)</f>
+        <v>1148406.1645999998</v>
+      </c>
+      <c r="E43" s="6">
+        <f t="shared" ref="E43:G43" si="6">AVERAGE(E39:E40)</f>
+        <v>5018.6110564800001</v>
+      </c>
+      <c r="F43" s="3">
+        <f t="shared" si="6"/>
+        <v>5.2278373753397389E-2</v>
+      </c>
+      <c r="G43" s="3">
+        <f t="shared" si="6"/>
+        <v>1.1837202763806765E-3</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B45" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D45" s="6">
+        <f>D42/D43</f>
+        <v>1.2800215472650383</v>
+      </c>
+      <c r="E45" s="6">
+        <f t="shared" ref="E45:G45" si="7">E42/E43</f>
+        <v>1.090543283688677</v>
+      </c>
+      <c r="F45" s="6">
+        <f t="shared" si="7"/>
+        <v>1.3904082000767517</v>
+      </c>
+      <c r="G45" s="6">
+        <f t="shared" si="7"/>
+        <v>1.297125195307224</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A47" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C47" s="2">
+        <v>2021</v>
+      </c>
+      <c r="D47" s="6">
+        <v>1730400.6762000001</v>
+      </c>
+      <c r="E47" s="6">
+        <v>11453.66344206</v>
+      </c>
+      <c r="F47" s="3">
+        <v>3.6351540108211508E-4</v>
+      </c>
+      <c r="G47" s="3">
+        <v>1.736681726385915E-4</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A48" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C48" s="2">
+        <v>2022</v>
+      </c>
+      <c r="D48" s="6">
+        <v>1665422.6664</v>
+      </c>
+      <c r="E48" s="6">
+        <v>8756.6848730599995</v>
+      </c>
+      <c r="F48" s="3">
+        <v>7.9418686213037007E-3</v>
+      </c>
+      <c r="G48" s="3">
+        <v>6.2767209962179716E-4</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A49" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C49" s="2">
+        <v>2023</v>
+      </c>
+      <c r="D49" s="6">
+        <v>1646977.0623999999</v>
+      </c>
+      <c r="E49" s="6">
+        <v>8501.7368701600008</v>
+      </c>
+      <c r="F49" s="3">
+        <v>3.13244725480416E-3</v>
+      </c>
+      <c r="G49" s="3">
+        <v>3.3557754651448161E-4</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A50" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C50" s="2">
+        <v>2024</v>
+      </c>
+      <c r="D50" s="6">
+        <v>1581936.48</v>
+      </c>
+      <c r="E50" s="6">
+        <v>7766.5038239999994</v>
+      </c>
+      <c r="F50" s="3">
+        <v>1.717868258658569E-2</v>
+      </c>
+      <c r="G50" s="3">
+        <v>1.213271790439538E-4</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B52" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="D52" s="6">
+        <f>AVERAGE(D47:D48)</f>
+        <v>1697911.6713</v>
+      </c>
+      <c r="E52" s="6">
+        <f t="shared" ref="E52:G52" si="8">AVERAGE(E47:E48)</f>
+        <v>10105.174157559999</v>
+      </c>
+      <c r="F52" s="3">
+        <f t="shared" si="8"/>
+        <v>4.1526920111929081E-3</v>
+      </c>
+      <c r="G52" s="3">
+        <f t="shared" si="8"/>
+        <v>4.0067013613019435E-4</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B53" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="D53" s="6">
+        <f>AVERAGE(D49:D50)</f>
+        <v>1614456.7711999998</v>
+      </c>
+      <c r="E53" s="6">
+        <f t="shared" ref="E53:G53" si="9">AVERAGE(E49:E50)</f>
+        <v>8134.1203470800001</v>
+      </c>
+      <c r="F53" s="3">
+        <f t="shared" si="9"/>
+        <v>1.0155564920694925E-2</v>
+      </c>
+      <c r="G53" s="3">
+        <f t="shared" si="9"/>
+        <v>2.2845236277921772E-4</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B55" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D55" s="6">
+        <f>D52/D53</f>
+        <v>1.0516922481844897</v>
+      </c>
+      <c r="E55" s="6">
+        <f t="shared" ref="E55:G55" si="10">E52/E53</f>
+        <v>1.2423192338416251</v>
+      </c>
+      <c r="F55" s="6">
+        <f t="shared" si="10"/>
+        <v>0.40890802664562625</v>
+      </c>
+      <c r="G55" s="6">
+        <f t="shared" si="10"/>
+        <v>1.7538454461835107</v>
+      </c>
+    </row>
   </sheetData>
   <sortState ref="A2:G17">
     <sortCondition descending="1" ref="D2:D17"/>
   </sortState>
   <conditionalFormatting sqref="D2:D17">
+    <cfRule type="colorScale" priority="32">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E2:E17">
+    <cfRule type="colorScale" priority="31">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F2:F17">
+    <cfRule type="colorScale" priority="30">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G2:G17">
+    <cfRule type="colorScale" priority="29">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D22:D23">
+    <cfRule type="colorScale" priority="28">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E22:E23">
+    <cfRule type="colorScale" priority="27">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F22:F23">
+    <cfRule type="colorScale" priority="26">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G22:G23">
+    <cfRule type="colorScale" priority="25">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D26:D29">
+    <cfRule type="colorScale" priority="24">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E26:E29">
+    <cfRule type="colorScale" priority="23">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F26:F29">
+    <cfRule type="colorScale" priority="22">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G26:G29">
+    <cfRule type="colorScale" priority="21">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D31:D32">
+    <cfRule type="colorScale" priority="20">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E31:E32">
+    <cfRule type="colorScale" priority="19">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F31:F32">
+    <cfRule type="colorScale" priority="18">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G31:G32">
+    <cfRule type="colorScale" priority="17">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D37:D40">
+    <cfRule type="colorScale" priority="16">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E37:E40">
+    <cfRule type="colorScale" priority="15">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F37:F40">
+    <cfRule type="colorScale" priority="14">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G37:G40">
+    <cfRule type="colorScale" priority="13">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D42:D43">
+    <cfRule type="colorScale" priority="12">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E42:E43">
+    <cfRule type="colorScale" priority="11">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F42:F43">
+    <cfRule type="colorScale" priority="10">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G42:G43">
+    <cfRule type="colorScale" priority="9">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D47:D50">
     <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="min"/>
@@ -990,7 +1767,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E17">
+  <conditionalFormatting sqref="E47:E50">
     <cfRule type="colorScale" priority="7">
       <colorScale>
         <cfvo type="min"/>
@@ -1002,7 +1779,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F17">
+  <conditionalFormatting sqref="F47:F50">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="min"/>
@@ -1014,7 +1791,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G17">
+  <conditionalFormatting sqref="G47:G50">
     <cfRule type="colorScale" priority="5">
       <colorScale>
         <cfvo type="min"/>
@@ -1026,7 +1803,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D22:D23">
+  <conditionalFormatting sqref="D52:D53">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="min"/>
@@ -1038,7 +1815,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E22:E23">
+  <conditionalFormatting sqref="E52:E53">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
@@ -1050,7 +1827,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F22:F23">
+  <conditionalFormatting sqref="F52:F53">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
@@ -1062,7 +1839,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G22:G23">
+  <conditionalFormatting sqref="G52:G53">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>

--- a/clustering/sepsectors/mining sector (factoriescap_s) 0.xlsx
+++ b/clustering/sepsectors/mining sector (factoriescap_s) 0.xlsx
@@ -14,12 +14,15 @@
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId2"/>
+  </externalReferences>
   <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="28">
   <si>
     <t>sector</t>
   </si>
@@ -100,6 +103,9 @@
   </si>
   <si>
     <t>разница</t>
+  </si>
+  <si>
+    <t>Year</t>
   </si>
 </sst>
 </file>
@@ -185,7 +191,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -204,6 +210,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -220,6 +229,3072 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ru-RU"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="1400" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:effectLst/>
+              </a:rPr>
+              <a:t>06</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ru-RU"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:radarChart>
+        <c:radarStyle val="marker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$C$44</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>0,90</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$D$43:$G$43</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>Year</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>ITcosts_s</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>skvozcosts_s</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>trainingcosts_s</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$D$44:$G$44</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.97861802384805219</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2.0280687025904316E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.40521795180340958</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-61E4-4428-B98A-36ED0CEBEA0B}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$C$47</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>1,00</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$D$43:$G$43</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>Year</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>ITcosts_s</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>skvozcosts_s</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>trainingcosts_s</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$D$47:$G$47</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.9065044697676391</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4.3827020054301634E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.53711582961067672</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-61E4-4428-B98A-36ED0CEBEA0B}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="744722240"/>
+        <c:axId val="744723072"/>
+      </c:radarChart>
+      <c:catAx>
+        <c:axId val="744722240"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="744723072"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="744723072"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1600" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="744722240"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="t"/>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ru-RU"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="ru-RU"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ru-RU"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="1400" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:effectLst/>
+              </a:rPr>
+              <a:t>07</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ru-RU"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:radarChart>
+        <c:radarStyle val="marker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$C$68</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>0,64</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$D$43:$G$43</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>Year</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>ITcosts_s</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>skvozcosts_s</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>trainingcosts_s</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$D$68:$G$68</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.28945244686889443</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.46185888639215267</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-FB7A-4E36-8F98-28BF4F7796B2}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$C$71</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>1,00</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$D$43:$G$43</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>Year</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>ITcosts_s</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>skvozcosts_s</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>trainingcosts_s</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$D$71:$G$71</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>0.25</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.98567037422891113</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.42098304385739743</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-FB7A-4E36-8F98-28BF4F7796B2}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="744722240"/>
+        <c:axId val="744723072"/>
+      </c:radarChart>
+      <c:catAx>
+        <c:axId val="744722240"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="744723072"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="744723072"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1600" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="744722240"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="t"/>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ru-RU"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="ru-RU"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ru-RU"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="1400" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:effectLst/>
+              </a:rPr>
+              <a:t>09</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ru-RU"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:radarChart>
+        <c:radarStyle val="marker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$C$92</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>0,91</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$D$43:$G$43</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>Year</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>ITcosts_s</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>skvozcosts_s</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>trainingcosts_s</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$D$92:$G$92</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.67808032454314493</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.19329707201747426</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-4DEB-4295-8E85-83ADBF1EE423}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$C$95</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>1,00</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$D$43:$G$43</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>Year</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>ITcosts_s</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>skvozcosts_s</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>trainingcosts_s</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$D$95:$G$95</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>0.25</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2.1160842762527853E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.2766861435186222</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-4DEB-4295-8E85-83ADBF1EE423}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="744722240"/>
+        <c:axId val="744723072"/>
+      </c:radarChart>
+      <c:catAx>
+        <c:axId val="744722240"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="744723072"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="744723072"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1600" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="744722240"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="t"/>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ru-RU"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="ru-RU"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="317">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="317">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="317">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>108858</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>40822</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>334459</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>176601</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Диаграмма 1"/>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>530679</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>27214</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>497746</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>162993</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Диаграмма 2"/>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>168088</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>179295</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>370479</xdr:colOff>
+      <xdr:row>59</xdr:row>
+      <xdr:rowOff>124574</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="Диаграмма 3"/>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="Original"/>
+      <sheetName val="Only best"/>
+      <sheetName val="Best|Worst"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="89">
+          <cell r="D89" t="str">
+            <v>Year</v>
+          </cell>
+          <cell r="E89" t="str">
+            <v>ITcosts_s</v>
+          </cell>
+          <cell r="F89" t="str">
+            <v>skvozcosts_s</v>
+          </cell>
+          <cell r="G89" t="str">
+            <v>trainingcosts_s</v>
+          </cell>
+        </row>
+        <row r="90">
+          <cell r="C90">
+            <v>0.60541707637600206</v>
+          </cell>
+          <cell r="D90">
+            <v>0.75</v>
+          </cell>
+          <cell r="E90">
+            <v>1</v>
+          </cell>
+          <cell r="F90">
+            <v>0.80661939562538798</v>
+          </cell>
+          <cell r="G90">
+            <v>0.45477225885659545</v>
+          </cell>
+        </row>
+        <row r="91">
+          <cell r="C91">
+            <v>0.62826451624711255</v>
+          </cell>
+          <cell r="D91">
+            <v>1</v>
+          </cell>
+          <cell r="E91">
+            <v>0.7323973572762863</v>
+          </cell>
+          <cell r="F91">
+            <v>0.9611546957323327</v>
+          </cell>
+          <cell r="G91">
+            <v>0.83771179639168136</v>
+          </cell>
+        </row>
+        <row r="92">
+          <cell r="C92">
+            <v>0.78924387345553881</v>
+          </cell>
+          <cell r="D92">
+            <v>0.5</v>
+          </cell>
+          <cell r="E92">
+            <v>0.90624842311195075</v>
+          </cell>
+          <cell r="F92">
+            <v>1</v>
+          </cell>
+          <cell r="G92">
+            <v>0.67809276193519175</v>
+          </cell>
+        </row>
+        <row r="93">
+          <cell r="C93">
+            <v>1</v>
+          </cell>
+          <cell r="D93">
+            <v>0.25</v>
+          </cell>
+          <cell r="E93">
+            <v>0.89882061387652312</v>
+          </cell>
+          <cell r="F93">
+            <v>0.17795127025264079</v>
+          </cell>
+          <cell r="G93">
+            <v>1</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -507,11 +3582,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J55"/>
+  <dimension ref="A1:J95"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="67" customWidth="1"/>
-    <col min="4" max="4" width="16.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.5703125" customWidth="1"/>
     <col min="5" max="5" width="16" customWidth="1"/>
     <col min="6" max="6" width="14" customWidth="1"/>
     <col min="7" max="7" width="14.85546875" customWidth="1"/>
@@ -998,6 +4073,23 @@
         <v>1.0604112949224313E-3</v>
       </c>
     </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C25" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>9</v>
@@ -1006,7 +4098,7 @@
         <v>10</v>
       </c>
       <c r="C26" s="2">
-        <v>2022</v>
+        <v>2</v>
       </c>
       <c r="D26" s="6">
         <v>12596210.486</v>
@@ -1029,7 +4121,7 @@
         <v>10</v>
       </c>
       <c r="C27" s="2">
-        <v>2021</v>
+        <v>1</v>
       </c>
       <c r="D27" s="6">
         <v>12460128.155999999</v>
@@ -1052,7 +4144,7 @@
         <v>10</v>
       </c>
       <c r="C28" s="2">
-        <v>2023</v>
+        <v>3</v>
       </c>
       <c r="D28" s="6">
         <v>11423484.0792</v>
@@ -1075,7 +4167,7 @@
         <v>10</v>
       </c>
       <c r="C29" s="2">
-        <v>2024</v>
+        <v>4</v>
       </c>
       <c r="D29" s="6">
         <v>11300772.48</v>
@@ -1132,7 +4224,7 @@
         <v>1.193064170373212E-3</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B34" s="7" t="s">
         <v>26</v>
       </c>
@@ -1153,319 +4245,955 @@
         <v>0.8055055175801521</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A37" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B37" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C37" s="2">
-        <v>2021</v>
-      </c>
-      <c r="D37" s="6">
-        <v>1743254.7426</v>
-      </c>
-      <c r="E37" s="6">
-        <v>5649.2667995399997</v>
-      </c>
-      <c r="F37" s="3">
-        <v>4.3069526144492228E-2</v>
-      </c>
-      <c r="G37" s="3">
-        <v>2.415866866318173E-3</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A38" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B38" s="2" t="s">
-        <v>12</v>
-      </c>
+    <row r="36" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C36" s="2">
+        <f>MAX(C26:C29)</f>
+        <v>4</v>
+      </c>
+      <c r="D36" s="2">
+        <f t="shared" ref="D36:G36" si="5">MAX(D26:D29)</f>
+        <v>12596210.486</v>
+      </c>
+      <c r="E36" s="2">
+        <f t="shared" si="5"/>
+        <v>32672.95173072</v>
+      </c>
+      <c r="F36" s="2">
+        <f t="shared" si="5"/>
+        <v>2.8388815641284579E-2</v>
+      </c>
+      <c r="G36" s="2">
+        <f t="shared" si="5"/>
+        <v>1.69804857508698E-3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C37" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F37" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G37" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="38" spans="2:7" x14ac:dyDescent="0.25">
       <c r="C38" s="2">
-        <v>2023</v>
-      </c>
-      <c r="D38" s="6">
-        <v>1196714.5288</v>
-      </c>
-      <c r="E38" s="6">
-        <v>5296.7583626400001</v>
-      </c>
-      <c r="F38" s="3">
-        <v>0.1023070329623097</v>
-      </c>
-      <c r="G38" s="3">
-        <v>6.5499992306063972E-4</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A39" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B39" s="2" t="s">
-        <v>12</v>
-      </c>
+        <f>C26/C$36</f>
+        <v>0.5</v>
+      </c>
+      <c r="D38" s="2">
+        <f t="shared" ref="D38:G38" si="6">D26/D$36</f>
+        <v>1</v>
+      </c>
+      <c r="E38" s="2">
+        <f t="shared" si="6"/>
+        <v>0.9065044697676391</v>
+      </c>
+      <c r="F38" s="2">
+        <f t="shared" si="6"/>
+        <v>4.3827020054301634E-2</v>
+      </c>
+      <c r="G38" s="2">
+        <f t="shared" si="6"/>
+        <v>0.53711582961067672</v>
+      </c>
+    </row>
+    <row r="39" spans="2:7" x14ac:dyDescent="0.25">
       <c r="C39" s="2">
-        <v>2024</v>
-      </c>
-      <c r="D39" s="6">
-        <v>1186586.3999999999</v>
-      </c>
-      <c r="E39" s="6">
-        <v>4305.8265600000004</v>
-      </c>
-      <c r="F39" s="3">
-        <v>7.4943726483957598E-2</v>
-      </c>
-      <c r="G39" s="3">
-        <v>1.251650972211942E-3</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A40" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B40" s="2" t="s">
-        <v>12</v>
-      </c>
+        <f t="shared" ref="C39:G41" si="7">C27/C$36</f>
+        <v>0.25</v>
+      </c>
+      <c r="D39" s="2">
+        <f t="shared" si="7"/>
+        <v>0.98919656589168237</v>
+      </c>
+      <c r="E39" s="2">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+      <c r="F39" s="2">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+      <c r="G39" s="2">
+        <f t="shared" si="7"/>
+        <v>0.5947949839696498</v>
+      </c>
+    </row>
+    <row r="40" spans="2:7" x14ac:dyDescent="0.25">
       <c r="C40" s="2">
-        <v>2022</v>
-      </c>
-      <c r="D40" s="6">
-        <v>1110225.9291999999</v>
-      </c>
-      <c r="E40" s="6">
-        <v>5731.3955529599998</v>
-      </c>
-      <c r="F40" s="3">
-        <v>2.961302102283718E-2</v>
-      </c>
-      <c r="G40" s="3">
-        <v>1.1157895805494109E-3</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B42" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="D42" s="6">
-        <f>AVERAGE(D37:D38)</f>
-        <v>1469984.6357</v>
-      </c>
-      <c r="E42" s="6">
-        <f t="shared" ref="E42:G42" si="5">AVERAGE(E37:E38)</f>
-        <v>5473.0125810899999</v>
-      </c>
-      <c r="F42" s="3">
-        <f t="shared" si="5"/>
-        <v>7.2688279553400958E-2</v>
-      </c>
-      <c r="G42" s="3">
-        <f t="shared" si="5"/>
-        <v>1.5354333946894063E-3</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B43" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="D43" s="6">
-        <f>AVERAGE(D39:D40)</f>
-        <v>1148406.1645999998</v>
-      </c>
-      <c r="E43" s="6">
-        <f t="shared" ref="E43:G43" si="6">AVERAGE(E39:E40)</f>
-        <v>5018.6110564800001</v>
-      </c>
-      <c r="F43" s="3">
-        <f t="shared" si="6"/>
-        <v>5.2278373753397389E-2</v>
-      </c>
-      <c r="G43" s="3">
-        <f t="shared" si="6"/>
-        <v>1.1837202763806765E-3</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B45" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="D45" s="6">
-        <f>D42/D43</f>
-        <v>1.2800215472650383</v>
-      </c>
-      <c r="E45" s="6">
-        <f t="shared" ref="E45:G45" si="7">E42/E43</f>
-        <v>1.090543283688677</v>
-      </c>
-      <c r="F45" s="6">
         <f t="shared" si="7"/>
-        <v>1.3904082000767517</v>
-      </c>
-      <c r="G45" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D40" s="2">
         <f t="shared" si="7"/>
-        <v>1.297125195307224</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A47" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B47" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C47" s="2">
-        <v>2021</v>
-      </c>
-      <c r="D47" s="6">
-        <v>1730400.6762000001</v>
-      </c>
-      <c r="E47" s="6">
-        <v>11453.66344206</v>
-      </c>
-      <c r="F47" s="3">
-        <v>3.6351540108211508E-4</v>
-      </c>
-      <c r="G47" s="3">
-        <v>1.736681726385915E-4</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A48" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B48" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C48" s="2">
-        <v>2022</v>
-      </c>
-      <c r="D48" s="6">
-        <v>1665422.6664</v>
-      </c>
-      <c r="E48" s="6">
-        <v>8756.6848730599995</v>
-      </c>
-      <c r="F48" s="3">
-        <v>7.9418686213037007E-3</v>
-      </c>
-      <c r="G48" s="3">
-        <v>6.2767209962179716E-4</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A49" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B49" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C49" s="2">
-        <v>2023</v>
-      </c>
-      <c r="D49" s="6">
-        <v>1646977.0623999999</v>
-      </c>
-      <c r="E49" s="6">
-        <v>8501.7368701600008</v>
-      </c>
-      <c r="F49" s="3">
-        <v>3.13244725480416E-3</v>
-      </c>
-      <c r="G49" s="3">
-        <v>3.3557754651448161E-4</v>
+        <v>0.90689847489422148</v>
+      </c>
+      <c r="E40" s="2">
+        <f t="shared" si="7"/>
+        <v>0.93602580402692193</v>
+      </c>
+      <c r="F40" s="2">
+        <f t="shared" si="7"/>
+        <v>3.0503494191693107E-3</v>
+      </c>
+      <c r="G40" s="2">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C41" s="2">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+      <c r="D41" s="2">
+        <f t="shared" si="7"/>
+        <v>0.89715652914503075</v>
+      </c>
+      <c r="E41" s="2">
+        <f t="shared" si="7"/>
+        <v>0.97861802384805219</v>
+      </c>
+      <c r="F41" s="2">
+        <f t="shared" si="7"/>
+        <v>2.0280687025904316E-2</v>
+      </c>
+      <c r="G41" s="2">
+        <f t="shared" si="7"/>
+        <v>0.40521795180340958</v>
+      </c>
+    </row>
+    <row r="43" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C43" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="D43" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="E43" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="F43" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="G43" s="8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="44" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C44" s="6">
+        <v>0.89715652914503075</v>
+      </c>
+      <c r="D44" s="2">
+        <v>1</v>
+      </c>
+      <c r="E44" s="2">
+        <v>0.97861802384805219</v>
+      </c>
+      <c r="F44" s="2">
+        <v>2.0280687025904316E-2</v>
+      </c>
+      <c r="G44" s="2">
+        <v>0.40521795180340958</v>
+      </c>
+    </row>
+    <row r="45" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C45" s="6">
+        <v>0.90689847489422148</v>
+      </c>
+      <c r="D45" s="2">
+        <v>0.75</v>
+      </c>
+      <c r="E45" s="2">
+        <v>0.93602580402692193</v>
+      </c>
+      <c r="F45" s="2">
+        <v>3.0503494191693107E-3</v>
+      </c>
+      <c r="G45" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C46" s="6">
+        <v>0.98919656589168237</v>
+      </c>
+      <c r="D46" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="E46" s="2">
+        <v>1</v>
+      </c>
+      <c r="F46" s="2">
+        <v>1</v>
+      </c>
+      <c r="G46" s="2">
+        <v>0.5947949839696498</v>
+      </c>
+    </row>
+    <row r="47" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C47" s="6">
+        <v>1</v>
+      </c>
+      <c r="D47" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="E47" s="2">
+        <v>0.9065044697676391</v>
+      </c>
+      <c r="F47" s="2">
+        <v>4.3827020054301634E-2</v>
+      </c>
+      <c r="G47" s="2">
+        <v>0.53711582961067672</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C50" s="2">
-        <v>2024</v>
+        <v>1</v>
       </c>
       <c r="D50" s="6">
-        <v>1581936.48</v>
+        <v>1743254.7426</v>
       </c>
       <c r="E50" s="6">
-        <v>7766.5038239999994</v>
+        <v>5649.2667995399997</v>
       </c>
       <c r="F50" s="3">
-        <v>1.717868258658569E-2</v>
+        <v>4.3069526144492228E-2</v>
       </c>
       <c r="G50" s="3">
-        <v>1.213271790439538E-4</v>
+        <v>2.415866866318173E-3</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A51" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C51" s="2">
+        <v>3</v>
+      </c>
+      <c r="D51" s="6">
+        <v>1196714.5288</v>
+      </c>
+      <c r="E51" s="6">
+        <v>5296.7583626400001</v>
+      </c>
+      <c r="F51" s="3">
+        <v>0.1023070329623097</v>
+      </c>
+      <c r="G51" s="3">
+        <v>6.5499992306063972E-4</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B52" s="7" t="s">
-        <v>24</v>
+      <c r="A52" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C52" s="2">
+        <v>4</v>
       </c>
       <c r="D52" s="6">
-        <f>AVERAGE(D47:D48)</f>
-        <v>1697911.6713</v>
+        <v>1186586.3999999999</v>
       </c>
       <c r="E52" s="6">
-        <f t="shared" ref="E52:G52" si="8">AVERAGE(E47:E48)</f>
-        <v>10105.174157559999</v>
+        <v>4305.8265600000004</v>
       </c>
       <c r="F52" s="3">
-        <f t="shared" si="8"/>
-        <v>4.1526920111929081E-3</v>
+        <v>7.4943726483957598E-2</v>
       </c>
       <c r="G52" s="3">
-        <f t="shared" si="8"/>
-        <v>4.0067013613019435E-4</v>
+        <v>1.251650972211942E-3</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B53" s="7" t="s">
-        <v>25</v>
+      <c r="A53" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C53" s="2">
+        <v>2</v>
       </c>
       <c r="D53" s="6">
-        <f>AVERAGE(D49:D50)</f>
-        <v>1614456.7711999998</v>
+        <v>1110225.9291999999</v>
       </c>
       <c r="E53" s="6">
-        <f t="shared" ref="E53:G53" si="9">AVERAGE(E49:E50)</f>
-        <v>8134.1203470800001</v>
+        <v>5731.3955529599998</v>
       </c>
       <c r="F53" s="3">
-        <f t="shared" si="9"/>
-        <v>1.0155564920694925E-2</v>
+        <v>2.961302102283718E-2</v>
       </c>
       <c r="G53" s="3">
-        <f t="shared" si="9"/>
-        <v>2.2845236277921772E-4</v>
+        <v>1.1157895805494109E-3</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B55" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="D55" s="6">
+        <f>AVERAGE(D50:D51)</f>
+        <v>1469984.6357</v>
+      </c>
+      <c r="E55" s="6">
+        <f t="shared" ref="E55:G55" si="8">AVERAGE(E50:E51)</f>
+        <v>5473.0125810899999</v>
+      </c>
+      <c r="F55" s="3">
+        <f t="shared" si="8"/>
+        <v>7.2688279553400958E-2</v>
+      </c>
+      <c r="G55" s="3">
+        <f t="shared" si="8"/>
+        <v>1.5354333946894063E-3</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B56" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="D56" s="6">
+        <f>AVERAGE(D52:D53)</f>
+        <v>1148406.1645999998</v>
+      </c>
+      <c r="E56" s="6">
+        <f t="shared" ref="E56:G56" si="9">AVERAGE(E52:E53)</f>
+        <v>5018.6110564800001</v>
+      </c>
+      <c r="F56" s="3">
+        <f t="shared" si="9"/>
+        <v>5.2278373753397389E-2</v>
+      </c>
+      <c r="G56" s="3">
+        <f t="shared" si="9"/>
+        <v>1.1837202763806765E-3</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B58" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="D55" s="6">
-        <f>D52/D53</f>
+      <c r="D58" s="6">
+        <f>D55/D56</f>
+        <v>1.2800215472650383</v>
+      </c>
+      <c r="E58" s="6">
+        <f t="shared" ref="E58:G58" si="10">E55/E56</f>
+        <v>1.090543283688677</v>
+      </c>
+      <c r="F58" s="6">
+        <f t="shared" si="10"/>
+        <v>1.3904082000767517</v>
+      </c>
+      <c r="G58" s="6">
+        <f t="shared" si="10"/>
+        <v>1.297125195307224</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C60" s="2">
+        <f>MAX(C50:C53)</f>
+        <v>4</v>
+      </c>
+      <c r="D60" s="2">
+        <f t="shared" ref="D60:G60" si="11">MAX(D50:D53)</f>
+        <v>1743254.7426</v>
+      </c>
+      <c r="E60" s="2">
+        <f t="shared" si="11"/>
+        <v>5731.3955529599998</v>
+      </c>
+      <c r="F60" s="2">
+        <f t="shared" si="11"/>
+        <v>0.1023070329623097</v>
+      </c>
+      <c r="G60" s="2">
+        <f t="shared" si="11"/>
+        <v>2.415866866318173E-3</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C61" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="D61" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E61" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F61" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G61" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C62" s="2">
+        <f>C50/C$60</f>
+        <v>0.25</v>
+      </c>
+      <c r="D62" s="2">
+        <f t="shared" ref="D62:G62" si="12">D50/D$60</f>
+        <v>1</v>
+      </c>
+      <c r="E62" s="2">
+        <f t="shared" si="12"/>
+        <v>0.98567037422891113</v>
+      </c>
+      <c r="F62" s="2">
+        <f t="shared" si="12"/>
+        <v>0.42098304385739743</v>
+      </c>
+      <c r="G62" s="2">
+        <f t="shared" si="12"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C63" s="2">
+        <f t="shared" ref="C63:G65" si="13">C51/C$60</f>
+        <v>0.75</v>
+      </c>
+      <c r="D63" s="2">
+        <f t="shared" si="13"/>
+        <v>0.68648287571278566</v>
+      </c>
+      <c r="E63" s="2">
+        <f t="shared" si="13"/>
+        <v>0.92416555683449042</v>
+      </c>
+      <c r="F63" s="2">
+        <f t="shared" si="13"/>
+        <v>1</v>
+      </c>
+      <c r="G63" s="2">
+        <f t="shared" si="13"/>
+        <v>0.27112417997555965</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C64" s="2">
+        <f t="shared" si="13"/>
+        <v>1</v>
+      </c>
+      <c r="D64" s="2">
+        <f t="shared" si="13"/>
+        <v>0.6806729796875528</v>
+      </c>
+      <c r="E64" s="2">
+        <f t="shared" si="13"/>
+        <v>0.75127017847795219</v>
+      </c>
+      <c r="F64" s="2">
+        <f t="shared" si="13"/>
+        <v>0.73253738588594541</v>
+      </c>
+      <c r="G64" s="2">
+        <f t="shared" si="13"/>
+        <v>0.51809600506648856</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C65" s="2">
+        <f t="shared" si="13"/>
+        <v>0.5</v>
+      </c>
+      <c r="D65" s="2">
+        <f t="shared" si="13"/>
+        <v>0.63686958771392121</v>
+      </c>
+      <c r="E65" s="2">
+        <f t="shared" si="13"/>
+        <v>1</v>
+      </c>
+      <c r="F65" s="2">
+        <f t="shared" si="13"/>
+        <v>0.28945244686889443</v>
+      </c>
+      <c r="G65" s="2">
+        <f t="shared" si="13"/>
+        <v>0.46185888639215267</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C67" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="D67" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="E67" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="F67" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="G67" s="8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C68" s="6">
+        <v>0.63686958771392121</v>
+      </c>
+      <c r="D68" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="E68" s="2">
+        <v>1</v>
+      </c>
+      <c r="F68" s="2">
+        <v>0.28945244686889443</v>
+      </c>
+      <c r="G68" s="2">
+        <v>0.46185888639215267</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C69" s="6">
+        <v>0.6806729796875528</v>
+      </c>
+      <c r="D69" s="2">
+        <v>1</v>
+      </c>
+      <c r="E69" s="2">
+        <v>0.75127017847795219</v>
+      </c>
+      <c r="F69" s="2">
+        <v>0.73253738588594541</v>
+      </c>
+      <c r="G69" s="2">
+        <v>0.51809600506648856</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C70" s="6">
+        <v>0.68648287571278566</v>
+      </c>
+      <c r="D70" s="2">
+        <v>0.75</v>
+      </c>
+      <c r="E70" s="2">
+        <v>0.92416555683449042</v>
+      </c>
+      <c r="F70" s="2">
+        <v>1</v>
+      </c>
+      <c r="G70" s="2">
+        <v>0.27112417997555965</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C71" s="6">
+        <v>1</v>
+      </c>
+      <c r="D71" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="E71" s="2">
+        <v>0.98567037422891113</v>
+      </c>
+      <c r="F71" s="2">
+        <v>0.42098304385739743</v>
+      </c>
+      <c r="G71" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A74" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C74" s="2">
+        <v>1</v>
+      </c>
+      <c r="D74" s="6">
+        <v>1730400.6762000001</v>
+      </c>
+      <c r="E74" s="6">
+        <v>11453.66344206</v>
+      </c>
+      <c r="F74" s="3">
+        <v>3.6351540108211508E-4</v>
+      </c>
+      <c r="G74" s="3">
+        <v>1.736681726385915E-4</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A75" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C75" s="2">
+        <v>2</v>
+      </c>
+      <c r="D75" s="6">
+        <v>1665422.6664</v>
+      </c>
+      <c r="E75" s="6">
+        <v>8756.6848730599995</v>
+      </c>
+      <c r="F75" s="3">
+        <v>7.9418686213037007E-3</v>
+      </c>
+      <c r="G75" s="3">
+        <v>6.2767209962179716E-4</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A76" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C76" s="2">
+        <v>3</v>
+      </c>
+      <c r="D76" s="6">
+        <v>1646977.0623999999</v>
+      </c>
+      <c r="E76" s="6">
+        <v>8501.7368701600008</v>
+      </c>
+      <c r="F76" s="3">
+        <v>3.13244725480416E-3</v>
+      </c>
+      <c r="G76" s="3">
+        <v>3.3557754651448161E-4</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A77" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B77" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C77" s="2">
+        <v>4</v>
+      </c>
+      <c r="D77" s="6">
+        <v>1581936.48</v>
+      </c>
+      <c r="E77" s="6">
+        <v>7766.5038239999994</v>
+      </c>
+      <c r="F77" s="3">
+        <v>1.717868258658569E-2</v>
+      </c>
+      <c r="G77" s="3">
+        <v>1.213271790439538E-4</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B79" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="D79" s="6">
+        <f>AVERAGE(D74:D75)</f>
+        <v>1697911.6713</v>
+      </c>
+      <c r="E79" s="6">
+        <f t="shared" ref="E79:G79" si="14">AVERAGE(E74:E75)</f>
+        <v>10105.174157559999</v>
+      </c>
+      <c r="F79" s="3">
+        <f t="shared" si="14"/>
+        <v>4.1526920111929081E-3</v>
+      </c>
+      <c r="G79" s="3">
+        <f t="shared" si="14"/>
+        <v>4.0067013613019435E-4</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B80" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="D80" s="6">
+        <f>AVERAGE(D76:D77)</f>
+        <v>1614456.7711999998</v>
+      </c>
+      <c r="E80" s="6">
+        <f t="shared" ref="E80:G80" si="15">AVERAGE(E76:E77)</f>
+        <v>8134.1203470800001</v>
+      </c>
+      <c r="F80" s="3">
+        <f t="shared" si="15"/>
+        <v>1.0155564920694925E-2</v>
+      </c>
+      <c r="G80" s="3">
+        <f t="shared" si="15"/>
+        <v>2.2845236277921772E-4</v>
+      </c>
+    </row>
+    <row r="82" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B82" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D82" s="6">
+        <f>D79/D80</f>
         <v>1.0516922481844897</v>
       </c>
-      <c r="E55" s="6">
-        <f t="shared" ref="E55:G55" si="10">E52/E53</f>
+      <c r="E82" s="6">
+        <f t="shared" ref="E82:G82" si="16">E79/E80</f>
         <v>1.2423192338416251</v>
       </c>
-      <c r="F55" s="6">
-        <f t="shared" si="10"/>
+      <c r="F82" s="6">
+        <f t="shared" si="16"/>
         <v>0.40890802664562625</v>
       </c>
-      <c r="G55" s="6">
-        <f t="shared" si="10"/>
+      <c r="G82" s="6">
+        <f t="shared" si="16"/>
         <v>1.7538454461835107</v>
       </c>
     </row>
+    <row r="84" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C84" s="2">
+        <f>MAX(C74:C77)</f>
+        <v>4</v>
+      </c>
+      <c r="D84" s="2">
+        <f t="shared" ref="D84:G84" si="17">MAX(D74:D77)</f>
+        <v>1730400.6762000001</v>
+      </c>
+      <c r="E84" s="2">
+        <f t="shared" si="17"/>
+        <v>11453.66344206</v>
+      </c>
+      <c r="F84" s="2">
+        <f t="shared" si="17"/>
+        <v>1.717868258658569E-2</v>
+      </c>
+      <c r="G84" s="2">
+        <f t="shared" si="17"/>
+        <v>6.2767209962179716E-4</v>
+      </c>
+    </row>
+    <row r="85" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C85" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="D85" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E85" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F85" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G85" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="86" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C86" s="2">
+        <f>C74/C$84</f>
+        <v>0.25</v>
+      </c>
+      <c r="D86" s="2">
+        <f t="shared" ref="D86:G86" si="18">D74/D$84</f>
+        <v>1</v>
+      </c>
+      <c r="E86" s="2">
+        <f t="shared" si="18"/>
+        <v>1</v>
+      </c>
+      <c r="F86" s="2">
+        <f t="shared" si="18"/>
+        <v>2.1160842762527853E-2</v>
+      </c>
+      <c r="G86" s="2">
+        <f t="shared" si="18"/>
+        <v>0.2766861435186222</v>
+      </c>
+    </row>
+    <row r="87" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C87" s="2">
+        <f t="shared" ref="C87:G89" si="19">C75/C$84</f>
+        <v>0.5</v>
+      </c>
+      <c r="D87" s="2">
+        <f t="shared" si="19"/>
+        <v>0.96244915371699158</v>
+      </c>
+      <c r="E87" s="2">
+        <f t="shared" si="19"/>
+        <v>0.76453135866589295</v>
+      </c>
+      <c r="F87" s="2">
+        <f t="shared" si="19"/>
+        <v>0.46230952701258149</v>
+      </c>
+      <c r="G87" s="2">
+        <f t="shared" si="19"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C88" s="2">
+        <f t="shared" si="19"/>
+        <v>0.75</v>
+      </c>
+      <c r="D88" s="2">
+        <f t="shared" si="19"/>
+        <v>0.95178942371705477</v>
+      </c>
+      <c r="E88" s="2">
+        <f t="shared" si="19"/>
+        <v>0.74227227935998441</v>
+      </c>
+      <c r="F88" s="2">
+        <f t="shared" si="19"/>
+        <v>0.18234502203621789</v>
+      </c>
+      <c r="G88" s="2">
+        <f t="shared" si="19"/>
+        <v>0.53463830352931618</v>
+      </c>
+    </row>
+    <row r="89" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C89" s="2">
+        <f t="shared" si="19"/>
+        <v>1</v>
+      </c>
+      <c r="D89" s="2">
+        <f t="shared" si="19"/>
+        <v>0.91420241667610136</v>
+      </c>
+      <c r="E89" s="2">
+        <f t="shared" si="19"/>
+        <v>0.67808032454314493</v>
+      </c>
+      <c r="F89" s="2">
+        <f t="shared" si="19"/>
+        <v>1</v>
+      </c>
+      <c r="G89" s="2">
+        <f t="shared" si="19"/>
+        <v>0.19329707201747426</v>
+      </c>
+    </row>
+    <row r="91" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C91" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="D91" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="E91" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="F91" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="G91" s="8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="92" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C92" s="6">
+        <v>0.91420241667610136</v>
+      </c>
+      <c r="D92" s="2">
+        <v>1</v>
+      </c>
+      <c r="E92" s="2">
+        <v>0.67808032454314493</v>
+      </c>
+      <c r="F92" s="2">
+        <v>1</v>
+      </c>
+      <c r="G92" s="2">
+        <v>0.19329707201747426</v>
+      </c>
+    </row>
+    <row r="93" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C93" s="6">
+        <v>0.95178942371705477</v>
+      </c>
+      <c r="D93" s="2">
+        <v>0.75</v>
+      </c>
+      <c r="E93" s="2">
+        <v>0.74227227935998441</v>
+      </c>
+      <c r="F93" s="2">
+        <v>0.18234502203621789</v>
+      </c>
+      <c r="G93" s="2">
+        <v>0.53463830352931618</v>
+      </c>
+    </row>
+    <row r="94" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C94" s="6">
+        <v>0.96244915371699158</v>
+      </c>
+      <c r="D94" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="E94" s="2">
+        <v>0.76453135866589295</v>
+      </c>
+      <c r="F94" s="2">
+        <v>0.46230952701258149</v>
+      </c>
+      <c r="G94" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="95" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C95" s="6">
+        <v>1</v>
+      </c>
+      <c r="D95" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="E95" s="2">
+        <v>1</v>
+      </c>
+      <c r="F95" s="2">
+        <v>2.1160842762527853E-2</v>
+      </c>
+      <c r="G95" s="2">
+        <v>0.2766861435186222</v>
+      </c>
+    </row>
   </sheetData>
-  <sortState ref="A2:G17">
-    <sortCondition descending="1" ref="D2:D17"/>
+  <sortState ref="C92:G95">
+    <sortCondition ref="C92:C95"/>
   </sortState>
   <conditionalFormatting sqref="D2:D17">
     <cfRule type="colorScale" priority="32">
@@ -1659,7 +5387,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D37:D40">
+  <conditionalFormatting sqref="D50:D53">
     <cfRule type="colorScale" priority="16">
       <colorScale>
         <cfvo type="min"/>
@@ -1671,7 +5399,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E37:E40">
+  <conditionalFormatting sqref="E50:E53">
     <cfRule type="colorScale" priority="15">
       <colorScale>
         <cfvo type="min"/>
@@ -1683,7 +5411,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F37:F40">
+  <conditionalFormatting sqref="F50:F53">
     <cfRule type="colorScale" priority="14">
       <colorScale>
         <cfvo type="min"/>
@@ -1695,7 +5423,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G37:G40">
+  <conditionalFormatting sqref="G50:G53">
     <cfRule type="colorScale" priority="13">
       <colorScale>
         <cfvo type="min"/>
@@ -1707,7 +5435,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D42:D43">
+  <conditionalFormatting sqref="D55:D56">
     <cfRule type="colorScale" priority="12">
       <colorScale>
         <cfvo type="min"/>
@@ -1719,7 +5447,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E42:E43">
+  <conditionalFormatting sqref="E55:E56">
     <cfRule type="colorScale" priority="11">
       <colorScale>
         <cfvo type="min"/>
@@ -1731,7 +5459,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F42:F43">
+  <conditionalFormatting sqref="F55:F56">
     <cfRule type="colorScale" priority="10">
       <colorScale>
         <cfvo type="min"/>
@@ -1743,7 +5471,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G42:G43">
+  <conditionalFormatting sqref="G55:G56">
     <cfRule type="colorScale" priority="9">
       <colorScale>
         <cfvo type="min"/>
@@ -1755,7 +5483,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D47:D50">
+  <conditionalFormatting sqref="D74:D77">
     <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="min"/>
@@ -1767,7 +5495,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E47:E50">
+  <conditionalFormatting sqref="E74:E77">
     <cfRule type="colorScale" priority="7">
       <colorScale>
         <cfvo type="min"/>
@@ -1779,7 +5507,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F47:F50">
+  <conditionalFormatting sqref="F74:F77">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="min"/>
@@ -1791,7 +5519,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G47:G50">
+  <conditionalFormatting sqref="G74:G77">
     <cfRule type="colorScale" priority="5">
       <colorScale>
         <cfvo type="min"/>
@@ -1803,7 +5531,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D52:D53">
+  <conditionalFormatting sqref="D79:D80">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="min"/>
@@ -1815,7 +5543,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E52:E53">
+  <conditionalFormatting sqref="E79:E80">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
@@ -1827,7 +5555,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F52:F53">
+  <conditionalFormatting sqref="F79:F80">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
@@ -1839,7 +5567,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G52:G53">
+  <conditionalFormatting sqref="G79:G80">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -1853,5 +5581,6 @@
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/clustering/sepsectors/mining sector (factoriescap_s) 0.xlsx
+++ b/clustering/sepsectors/mining sector (factoriescap_s) 0.xlsx
@@ -14,15 +14,12 @@
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId2"/>
-  </externalReferences>
   <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="30">
   <si>
     <t>sector</t>
   </si>
@@ -107,6 +104,12 @@
   <si>
     <t>Year</t>
   </si>
+  <si>
+    <t>best</t>
+  </si>
+  <si>
+    <t>worst</t>
+  </si>
 </sst>
 </file>
 
@@ -115,12 +118,20 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.000%"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -189,11 +200,11 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -202,15 +213,18 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -3100,16 +3114,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>108858</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>40822</xdr:rowOff>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>247403</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>6185</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>334459</xdr:colOff>
-      <xdr:row>35</xdr:row>
-      <xdr:rowOff>176601</xdr:rowOff>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>230550</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>141964</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -3132,16 +3146,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>530679</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>27214</xdr:rowOff>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>357497</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>44533</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>25</xdr:col>
-      <xdr:colOff>497746</xdr:colOff>
-      <xdr:row>35</xdr:row>
-      <xdr:rowOff>162993</xdr:rowOff>
+      <xdr:col>30</xdr:col>
+      <xdr:colOff>324564</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>180312</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -3164,15 +3178,15 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>168088</xdr:colOff>
-      <xdr:row>36</xdr:row>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>289315</xdr:colOff>
+      <xdr:row>35</xdr:row>
       <xdr:rowOff>179295</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>370479</xdr:colOff>
-      <xdr:row>59</xdr:row>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>249252</xdr:colOff>
+      <xdr:row>58</xdr:row>
       <xdr:rowOff>124574</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -3195,106 +3209,6 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
-</file>
-
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="Original"/>
-      <sheetName val="Only best"/>
-      <sheetName val="Best|Worst"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="89">
-          <cell r="D89" t="str">
-            <v>Year</v>
-          </cell>
-          <cell r="E89" t="str">
-            <v>ITcosts_s</v>
-          </cell>
-          <cell r="F89" t="str">
-            <v>skvozcosts_s</v>
-          </cell>
-          <cell r="G89" t="str">
-            <v>trainingcosts_s</v>
-          </cell>
-        </row>
-        <row r="90">
-          <cell r="C90">
-            <v>0.60541707637600206</v>
-          </cell>
-          <cell r="D90">
-            <v>0.75</v>
-          </cell>
-          <cell r="E90">
-            <v>1</v>
-          </cell>
-          <cell r="F90">
-            <v>0.80661939562538798</v>
-          </cell>
-          <cell r="G90">
-            <v>0.45477225885659545</v>
-          </cell>
-        </row>
-        <row r="91">
-          <cell r="C91">
-            <v>0.62826451624711255</v>
-          </cell>
-          <cell r="D91">
-            <v>1</v>
-          </cell>
-          <cell r="E91">
-            <v>0.7323973572762863</v>
-          </cell>
-          <cell r="F91">
-            <v>0.9611546957323327</v>
-          </cell>
-          <cell r="G91">
-            <v>0.83771179639168136</v>
-          </cell>
-        </row>
-        <row r="92">
-          <cell r="C92">
-            <v>0.78924387345553881</v>
-          </cell>
-          <cell r="D92">
-            <v>0.5</v>
-          </cell>
-          <cell r="E92">
-            <v>0.90624842311195075</v>
-          </cell>
-          <cell r="F92">
-            <v>1</v>
-          </cell>
-          <cell r="G92">
-            <v>0.67809276193519175</v>
-          </cell>
-        </row>
-        <row r="93">
-          <cell r="C93">
-            <v>1</v>
-          </cell>
-          <cell r="D93">
-            <v>0.25</v>
-          </cell>
-          <cell r="E93">
-            <v>0.89882061387652312</v>
-          </cell>
-          <cell r="F93">
-            <v>0.17795127025264079</v>
-          </cell>
-          <cell r="G93">
-            <v>1</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3582,7 +3496,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J95"/>
+  <dimension ref="A1:L114"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="67" customWidth="1"/>
@@ -3590,7 +3504,7 @@
     <col min="5" max="5" width="16" customWidth="1"/>
     <col min="6" max="6" width="14" customWidth="1"/>
     <col min="7" max="7" width="14.85546875" customWidth="1"/>
-    <col min="9" max="9" width="14.5703125" customWidth="1"/>
+    <col min="9" max="9" width="10" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -4224,7 +4138,7 @@
         <v>1.193064170373212E-3</v>
       </c>
     </row>
-    <row r="34" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B34" s="7" t="s">
         <v>26</v>
       </c>
@@ -4244,8 +4158,26 @@
         <f t="shared" si="4"/>
         <v>0.8055055175801521</v>
       </c>
-    </row>
-    <row r="36" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="J34" s="8"/>
+      <c r="K34" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="L34" s="8" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="35" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="J35" s="8">
+        <v>6</v>
+      </c>
+      <c r="K35" s="9">
+        <v>0.3925398627504042</v>
+      </c>
+      <c r="L35" s="9">
+        <v>0.70595055998441802</v>
+      </c>
+    </row>
+    <row r="36" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C36" s="2">
         <f>MAX(C26:C29)</f>
         <v>4</v>
@@ -4266,8 +4198,17 @@
         <f t="shared" si="5"/>
         <v>1.69804857508698E-3</v>
       </c>
-    </row>
-    <row r="37" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="J36" s="8">
+        <v>7</v>
+      </c>
+      <c r="K36" s="6">
+        <v>0.66617557589878618</v>
+      </c>
+      <c r="L36" s="6">
+        <v>0.57703403741966097</v>
+      </c>
+    </row>
+    <row r="37" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C37" s="8" t="s">
         <v>27</v>
       </c>
@@ -4283,8 +4224,17 @@
       <c r="G37" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="38" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="J37" s="8">
+        <v>9</v>
+      </c>
+      <c r="K37" s="6">
+        <v>0.17309364530987559</v>
+      </c>
+      <c r="L37" s="6">
+        <v>0.87137739656061919</v>
+      </c>
+    </row>
+    <row r="38" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C38" s="2">
         <f>C26/C$36</f>
         <v>0.5</v>
@@ -4306,7 +4256,7 @@
         <v>0.53711582961067672</v>
       </c>
     </row>
-    <row r="39" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C39" s="2">
         <f t="shared" ref="C39:G41" si="7">C27/C$36</f>
         <v>0.25</v>
@@ -4328,7 +4278,7 @@
         <v>0.5947949839696498</v>
       </c>
     </row>
-    <row r="40" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C40" s="2">
         <f t="shared" si="7"/>
         <v>0.75</v>
@@ -4350,7 +4300,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C41" s="2">
         <f t="shared" si="7"/>
         <v>1</v>
@@ -4372,7 +4322,7 @@
         <v>0.40521795180340958</v>
       </c>
     </row>
-    <row r="43" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C43" s="8" t="s">
         <v>3</v>
       </c>
@@ -4389,7 +4339,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="44" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C44" s="6">
         <v>0.89715652914503075</v>
       </c>
@@ -4406,7 +4356,7 @@
         <v>0.40521795180340958</v>
       </c>
     </row>
-    <row r="45" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C45" s="6">
         <v>0.90689847489422148</v>
       </c>
@@ -4423,7 +4373,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C46" s="6">
         <v>0.98919656589168237</v>
       </c>
@@ -4440,7 +4390,7 @@
         <v>0.5947949839696498</v>
       </c>
     </row>
-    <row r="47" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C47" s="6">
         <v>1</v>
       </c>
@@ -4457,7 +4407,7 @@
         <v>0.53711582961067672</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
         <v>11</v>
       </c>
@@ -4480,7 +4430,7 @@
         <v>2.415866866318173E-3</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
         <v>11</v>
       </c>
@@ -4503,7 +4453,7 @@
         <v>6.5499992306063972E-4</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
         <v>11</v>
       </c>
@@ -4526,7 +4476,7 @@
         <v>1.251650972211942E-3</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
         <v>11</v>
       </c>
@@ -4549,7 +4499,7 @@
         <v>1.1157895805494109E-3</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B55" s="7" t="s">
         <v>24</v>
       </c>
@@ -4570,7 +4520,7 @@
         <v>1.5354333946894063E-3</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B56" s="7" t="s">
         <v>25</v>
       </c>
@@ -4591,7 +4541,7 @@
         <v>1.1837202763806765E-3</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B58" s="7" t="s">
         <v>26</v>
       </c>
@@ -4612,7 +4562,7 @@
         <v>1.297125195307224</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C60" s="2">
         <f>MAX(C50:C53)</f>
         <v>4</v>
@@ -4634,7 +4584,7 @@
         <v>2.415866866318173E-3</v>
       </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C61" s="8" t="s">
         <v>27</v>
       </c>
@@ -4650,8 +4600,15 @@
       <c r="G61" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="J61" s="2"/>
+      <c r="K61" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="L61" s="8" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="62" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C62" s="2">
         <f>C50/C$60</f>
         <v>0.25</v>
@@ -4672,8 +4629,19 @@
         <f t="shared" si="12"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="J62" s="8">
+        <v>6</v>
+      </c>
+      <c r="K62" s="6">
+        <f>0.5*(D47*E47+E47*F47+F47*G47+G47*D47)</f>
+        <v>0.3925398627504042</v>
+      </c>
+      <c r="L62" s="6">
+        <f>0.5*(D44*E44+E44*F44+F44*G44+G44*D44)</f>
+        <v>0.70595055998441802</v>
+      </c>
+    </row>
+    <row r="63" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C63" s="2">
         <f t="shared" ref="C63:G65" si="13">C51/C$60</f>
         <v>0.75</v>
@@ -4695,7 +4663,7 @@
         <v>0.27112417997555965</v>
       </c>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C64" s="2">
         <f t="shared" si="13"/>
         <v>1</v>
@@ -4958,7 +4926,7 @@
         <v>2.2845236277921772E-4</v>
       </c>
     </row>
-    <row r="82" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="82" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B82" s="7" t="s">
         <v>26</v>
       </c>
@@ -4979,7 +4947,7 @@
         <v>1.7538454461835107</v>
       </c>
     </row>
-    <row r="84" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="84" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C84" s="2">
         <f>MAX(C74:C77)</f>
         <v>4</v>
@@ -5000,8 +4968,11 @@
         <f t="shared" si="17"/>
         <v>6.2767209962179716E-4</v>
       </c>
-    </row>
-    <row r="85" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="J84" s="2"/>
+      <c r="K84" s="8"/>
+      <c r="L84" s="8"/>
+    </row>
+    <row r="85" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C85" s="8" t="s">
         <v>27</v>
       </c>
@@ -5017,96 +4988,114 @@
       <c r="G85" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="86" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="J85" s="2"/>
+      <c r="K85" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="L85" s="8" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="86" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C86" s="2">
         <f>C74/C$84</f>
         <v>0.25</v>
       </c>
       <c r="D86" s="2">
-        <f t="shared" ref="D86:G86" si="18">D74/D$84</f>
+        <f>D74/D$84</f>
         <v>1</v>
       </c>
       <c r="E86" s="2">
-        <f t="shared" si="18"/>
+        <f>E74/E$84</f>
         <v>1</v>
       </c>
       <c r="F86" s="2">
-        <f t="shared" si="18"/>
+        <f>F74/F$84</f>
         <v>2.1160842762527853E-2</v>
       </c>
       <c r="G86" s="2">
-        <f t="shared" si="18"/>
+        <f>G74/G$84</f>
         <v>0.2766861435186222</v>
       </c>
-    </row>
-    <row r="87" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="J86" s="8">
+        <v>7</v>
+      </c>
+      <c r="K86" s="6">
+        <f>0.5*(D71*E71+E71*F71+F71*G71+G71*D71)</f>
+        <v>0.66617557589878618</v>
+      </c>
+      <c r="L86" s="6">
+        <f>0.5*(D68*E68+E68*F68+F68*G68+G68*D68)</f>
+        <v>0.57703403741966097</v>
+      </c>
+    </row>
+    <row r="87" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C87" s="2">
-        <f t="shared" ref="C87:G89" si="19">C75/C$84</f>
+        <f>C75/C$84</f>
         <v>0.5</v>
       </c>
       <c r="D87" s="2">
-        <f t="shared" si="19"/>
+        <f>D75/D$84</f>
         <v>0.96244915371699158</v>
       </c>
       <c r="E87" s="2">
-        <f t="shared" si="19"/>
+        <f>E75/E$84</f>
         <v>0.76453135866589295</v>
       </c>
       <c r="F87" s="2">
-        <f t="shared" si="19"/>
+        <f>F75/F$84</f>
         <v>0.46230952701258149</v>
       </c>
       <c r="G87" s="2">
-        <f t="shared" si="19"/>
+        <f>G75/G$84</f>
         <v>1</v>
       </c>
     </row>
-    <row r="88" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="88" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C88" s="2">
-        <f t="shared" si="19"/>
+        <f>C76/C$84</f>
         <v>0.75</v>
       </c>
       <c r="D88" s="2">
-        <f t="shared" si="19"/>
+        <f>D76/D$84</f>
         <v>0.95178942371705477</v>
       </c>
       <c r="E88" s="2">
-        <f t="shared" si="19"/>
+        <f>E76/E$84</f>
         <v>0.74227227935998441</v>
       </c>
       <c r="F88" s="2">
-        <f t="shared" si="19"/>
+        <f>F76/F$84</f>
         <v>0.18234502203621789</v>
       </c>
       <c r="G88" s="2">
-        <f t="shared" si="19"/>
+        <f>G76/G$84</f>
         <v>0.53463830352931618</v>
       </c>
     </row>
-    <row r="89" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="89" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C89" s="2">
-        <f t="shared" si="19"/>
+        <f>C77/C$84</f>
         <v>1</v>
       </c>
       <c r="D89" s="2">
-        <f t="shared" si="19"/>
+        <f>D77/D$84</f>
         <v>0.91420241667610136</v>
       </c>
       <c r="E89" s="2">
-        <f t="shared" si="19"/>
+        <f>E77/E$84</f>
         <v>0.67808032454314493</v>
       </c>
       <c r="F89" s="2">
-        <f t="shared" si="19"/>
+        <f>F77/F$84</f>
         <v>1</v>
       </c>
       <c r="G89" s="2">
-        <f t="shared" si="19"/>
+        <f>G77/G$84</f>
         <v>0.19329707201747426</v>
       </c>
     </row>
-    <row r="91" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="91" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C91" s="8" t="s">
         <v>3</v>
       </c>
@@ -5123,7 +5112,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="92" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="92" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C92" s="6">
         <v>0.91420241667610136</v>
       </c>
@@ -5140,7 +5129,7 @@
         <v>0.19329707201747426</v>
       </c>
     </row>
-    <row r="93" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="93" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C93" s="6">
         <v>0.95178942371705477</v>
       </c>
@@ -5157,7 +5146,7 @@
         <v>0.53463830352931618</v>
       </c>
     </row>
-    <row r="94" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="94" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C94" s="6">
         <v>0.96244915371699158</v>
       </c>
@@ -5174,7 +5163,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="95" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="95" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C95" s="6">
         <v>1</v>
       </c>
@@ -5190,6 +5179,58 @@
       <c r="G95" s="2">
         <v>0.2766861435186222</v>
       </c>
+    </row>
+    <row r="103" spans="10:12" x14ac:dyDescent="0.25">
+      <c r="J103" s="2"/>
+      <c r="K103" s="8"/>
+      <c r="L103" s="8"/>
+    </row>
+    <row r="104" spans="10:12" x14ac:dyDescent="0.25">
+      <c r="J104" s="8"/>
+      <c r="K104" s="6"/>
+      <c r="L104" s="6"/>
+    </row>
+    <row r="106" spans="10:12" x14ac:dyDescent="0.25">
+      <c r="J106" s="2"/>
+      <c r="K106" s="8"/>
+      <c r="L106" s="8"/>
+    </row>
+    <row r="107" spans="10:12" x14ac:dyDescent="0.25">
+      <c r="J107" s="8"/>
+      <c r="K107" s="6"/>
+      <c r="L107" s="6"/>
+    </row>
+    <row r="109" spans="10:12" x14ac:dyDescent="0.25">
+      <c r="J109" s="2"/>
+      <c r="K109" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="L109" s="8" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="110" spans="10:12" x14ac:dyDescent="0.25">
+      <c r="J110" s="8">
+        <v>9</v>
+      </c>
+      <c r="K110" s="6">
+        <f>0.5*(D95*E95+E95*F95+F95*G95+G95*D95)</f>
+        <v>0.17309364530987559</v>
+      </c>
+      <c r="L110" s="6">
+        <f>0.5*(D92*E92+E92*F92+F92*G92+G92*D92)</f>
+        <v>0.87137739656061919</v>
+      </c>
+    </row>
+    <row r="113" spans="10:12" x14ac:dyDescent="0.25">
+      <c r="J113" s="2"/>
+      <c r="K113" s="8"/>
+      <c r="L113" s="8"/>
+    </row>
+    <row r="114" spans="10:12" x14ac:dyDescent="0.25">
+      <c r="J114" s="8"/>
+      <c r="K114" s="6"/>
+      <c r="L114" s="6"/>
     </row>
   </sheetData>
   <sortState ref="C92:G95">

--- a/clustering/sepsectors/mining sector (factoriescap_s) 0.xlsx
+++ b/clustering/sepsectors/mining sector (factoriescap_s) 0.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12885"/>
+    <workbookView minimized="1" xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12885"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="31">
   <si>
     <t>sector</t>
   </si>
@@ -109,6 +109,9 @@
   </si>
   <si>
     <t>worst</t>
+  </si>
+  <si>
+    <t>сред</t>
   </si>
 </sst>
 </file>
@@ -4277,6 +4280,17 @@
         <f t="shared" si="7"/>
         <v>0.5947949839696498</v>
       </c>
+      <c r="J39" t="s">
+        <v>30</v>
+      </c>
+      <c r="K39" s="6">
+        <f>AVERAGE(K35:K37)</f>
+        <v>0.41060302798635534</v>
+      </c>
+      <c r="L39" s="6">
+        <f>AVERAGE(L35:L37)</f>
+        <v>0.71812066465489943</v>
+      </c>
     </row>
     <row r="40" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C40" s="2">
@@ -4998,23 +5012,23 @@
     </row>
     <row r="86" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C86" s="2">
-        <f>C74/C$84</f>
+        <f t="shared" ref="C86:G89" si="18">C74/C$84</f>
         <v>0.25</v>
       </c>
       <c r="D86" s="2">
-        <f>D74/D$84</f>
+        <f t="shared" si="18"/>
         <v>1</v>
       </c>
       <c r="E86" s="2">
-        <f>E74/E$84</f>
+        <f t="shared" si="18"/>
         <v>1</v>
       </c>
       <c r="F86" s="2">
-        <f>F74/F$84</f>
+        <f t="shared" si="18"/>
         <v>2.1160842762527853E-2</v>
       </c>
       <c r="G86" s="2">
-        <f>G74/G$84</f>
+        <f t="shared" si="18"/>
         <v>0.2766861435186222</v>
       </c>
       <c r="J86" s="8">
@@ -5031,67 +5045,67 @@
     </row>
     <row r="87" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C87" s="2">
-        <f>C75/C$84</f>
+        <f t="shared" si="18"/>
         <v>0.5</v>
       </c>
       <c r="D87" s="2">
-        <f>D75/D$84</f>
+        <f t="shared" si="18"/>
         <v>0.96244915371699158</v>
       </c>
       <c r="E87" s="2">
-        <f>E75/E$84</f>
+        <f t="shared" si="18"/>
         <v>0.76453135866589295</v>
       </c>
       <c r="F87" s="2">
-        <f>F75/F$84</f>
+        <f t="shared" si="18"/>
         <v>0.46230952701258149</v>
       </c>
       <c r="G87" s="2">
-        <f>G75/G$84</f>
+        <f t="shared" si="18"/>
         <v>1</v>
       </c>
     </row>
     <row r="88" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C88" s="2">
-        <f>C76/C$84</f>
+        <f t="shared" si="18"/>
         <v>0.75</v>
       </c>
       <c r="D88" s="2">
-        <f>D76/D$84</f>
+        <f t="shared" si="18"/>
         <v>0.95178942371705477</v>
       </c>
       <c r="E88" s="2">
-        <f>E76/E$84</f>
+        <f t="shared" si="18"/>
         <v>0.74227227935998441</v>
       </c>
       <c r="F88" s="2">
-        <f>F76/F$84</f>
+        <f t="shared" si="18"/>
         <v>0.18234502203621789</v>
       </c>
       <c r="G88" s="2">
-        <f>G76/G$84</f>
+        <f t="shared" si="18"/>
         <v>0.53463830352931618</v>
       </c>
     </row>
     <row r="89" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C89" s="2">
-        <f>C77/C$84</f>
+        <f t="shared" si="18"/>
         <v>1</v>
       </c>
       <c r="D89" s="2">
-        <f>D77/D$84</f>
+        <f t="shared" si="18"/>
         <v>0.91420241667610136</v>
       </c>
       <c r="E89" s="2">
-        <f>E77/E$84</f>
+        <f t="shared" si="18"/>
         <v>0.67808032454314493</v>
       </c>
       <c r="F89" s="2">
-        <f>F77/F$84</f>
+        <f t="shared" si="18"/>
         <v>1</v>
       </c>
       <c r="G89" s="2">
-        <f>G77/G$84</f>
+        <f t="shared" si="18"/>
         <v>0.19329707201747426</v>
       </c>
     </row>

--- a/clustering/sepsectors/mining sector (factoriescap_s) 0.xlsx
+++ b/clustering/sepsectors/mining sector (factoriescap_s) 0.xlsx
@@ -9,17 +9,21 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView minimized="1" xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12885"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12885" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1 (2)" sheetId="2" r:id="rId2"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId3"/>
+  </externalReferences>
   <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="31">
   <si>
     <t>sector</t>
   </si>
@@ -1478,6 +1482,1197 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ru-RU"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>06</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ru-RU"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:radarChart>
+        <c:radarStyle val="marker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Sheet1 (2)'!$C$44</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>0,90</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Sheet1 (2)'!$E$43:$G$43</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>ITcosts_s</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>skvozcosts_s</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>trainingcosts_s</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Sheet1 (2)'!$E$44:$G$44</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>0.97861802384805219</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2.0280687025904316E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.40521795180340958</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-9F33-401D-896B-29422D1EEA5F}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Sheet1 (2)'!$C$47</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>1,00</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Sheet1 (2)'!$E$43:$G$43</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>ITcosts_s</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>skvozcosts_s</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>trainingcosts_s</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Sheet1 (2)'!$E$47:$G$47</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>0.9065044697676391</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>4.3827020054301634E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.53711582961067672</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-9F33-401D-896B-29422D1EEA5F}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="285497360"/>
+        <c:axId val="285495696"/>
+      </c:radarChart>
+      <c:catAx>
+        <c:axId val="285497360"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="285495696"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="285495696"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="285497360"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="t"/>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ru-RU"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="ru-RU"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ru-RU"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>07</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ru-RU"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:radarChart>
+        <c:radarStyle val="marker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Sheet1 (2)'!$C$68</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>0,64</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Sheet1 (2)'!$E$43:$G$43</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>ITcosts_s</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>skvozcosts_s</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>trainingcosts_s</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Sheet1 (2)'!$E$68:$G$68</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.28945244686889443</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.46185888639215267</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-14BB-4D10-910B-9A775C976D8A}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Sheet1 (2)'!$C$71</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>1,00</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Sheet1 (2)'!$E$43:$G$43</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>ITcosts_s</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>skvozcosts_s</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>trainingcosts_s</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Sheet1 (2)'!$E$71:$G$71</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>0.98567037422891113</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.42098304385739743</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-14BB-4D10-910B-9A775C976D8A}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="285497360"/>
+        <c:axId val="285495696"/>
+      </c:radarChart>
+      <c:catAx>
+        <c:axId val="285497360"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="285495696"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="285495696"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="285497360"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="t"/>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ru-RU"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="ru-RU"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ru-RU"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>09</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ru-RU"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:radarChart>
+        <c:radarStyle val="marker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Sheet1 (2)'!$C$92</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>0,91</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Sheet1 (2)'!$E$43:$G$43</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>ITcosts_s</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>skvozcosts_s</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>trainingcosts_s</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Sheet1 (2)'!$E$92:$G$92</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>0.67808032454314493</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.19329707201747426</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-953F-4E74-B776-89AA4B4764CB}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Sheet1 (2)'!$C$95</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>1,00</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Sheet1 (2)'!$E$43:$G$43</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>ITcosts_s</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>skvozcosts_s</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>trainingcosts_s</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Sheet1 (2)'!$E$95:$G$95</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2.1160842762527853E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.2766861435186222</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-953F-4E74-B776-89AA4B4764CB}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="285497360"/>
+        <c:axId val="285495696"/>
+      </c:radarChart>
+      <c:catAx>
+        <c:axId val="285497360"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="285495696"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="285495696"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="285497360"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="t"/>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ru-RU"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="ru-RU"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
@@ -1598,6 +2793,126 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors5.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors6.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="317">
   <cs:axisTitle>
@@ -2609,6 +3924,1521 @@
 </file>
 
 <file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="317">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="317">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style5.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="317">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style6.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="317">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -3212,6 +6042,190 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>138545</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>86591</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>82880</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>133351</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="5" name="Диаграмма 4"/>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>363682</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>86590</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>30</xdr:col>
+      <xdr:colOff>308017</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="6" name="Диаграмма 5"/>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>277091</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>138545</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>221426</xdr:colOff>
+      <xdr:row>59</xdr:row>
+      <xdr:rowOff>185305</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="7" name="Диаграмма 6"/>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="Sheet1"/>
+      <sheetName val="Sheet1 (2)"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1">
+        <row r="42">
+          <cell r="E42" t="str">
+            <v>ITcosts_s</v>
+          </cell>
+          <cell r="F42" t="str">
+            <v>skvozcosts_s</v>
+          </cell>
+          <cell r="G42" t="str">
+            <v>trainingcosts_s</v>
+          </cell>
+        </row>
+        <row r="43">
+          <cell r="C43">
+            <v>0.53195397442833625</v>
+          </cell>
+          <cell r="E43">
+            <v>1</v>
+          </cell>
+          <cell r="F43">
+            <v>0.4341128768543896</v>
+          </cell>
+          <cell r="G43">
+            <v>0.96268324181002174</v>
+          </cell>
+        </row>
+        <row r="44">
+          <cell r="C44">
+            <v>0.74071957251902487</v>
+          </cell>
+          <cell r="E44">
+            <v>0.81436789578742097</v>
+          </cell>
+          <cell r="F44">
+            <v>1</v>
+          </cell>
+          <cell r="G44">
+            <v>1</v>
+          </cell>
+        </row>
+        <row r="45">
+          <cell r="C45">
+            <v>0.88899585107146872</v>
+          </cell>
+          <cell r="E45">
+            <v>0.3732928962109599</v>
+          </cell>
+          <cell r="F45">
+            <v>0.78623653793827153</v>
+          </cell>
+          <cell r="G45">
+            <v>0.50683853134311552</v>
+          </cell>
+        </row>
+        <row r="46">
+          <cell r="C46">
+            <v>1</v>
+          </cell>
+          <cell r="E46">
+            <v>0.37449706271284755</v>
+          </cell>
+          <cell r="F46">
+            <v>0.59247665944601891</v>
+          </cell>
+          <cell r="G46">
+            <v>0.50683853134311552</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5638,4 +8652,2144 @@
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:L114"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="67" customWidth="1"/>
+    <col min="4" max="4" width="15.5703125" customWidth="1"/>
+    <col min="5" max="5" width="16" customWidth="1"/>
+    <col min="6" max="6" width="14" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" customWidth="1"/>
+    <col min="9" max="9" width="10" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" s="2">
+        <v>2022</v>
+      </c>
+      <c r="D2" s="2">
+        <v>12596210.486</v>
+      </c>
+      <c r="E2" s="2">
+        <v>29618.176784399999</v>
+      </c>
+      <c r="F2" s="3">
+        <v>1.244197192428451E-3</v>
+      </c>
+      <c r="G2" s="3">
+        <v>9.1204876912707078E-4</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="2">
+        <v>2021</v>
+      </c>
+      <c r="D3" s="2">
+        <v>12460128.155999999</v>
+      </c>
+      <c r="E3" s="2">
+        <v>32672.95173072</v>
+      </c>
+      <c r="F3" s="3">
+        <v>2.8388815641284579E-2</v>
+      </c>
+      <c r="G3" s="3">
+        <v>1.009990774998547E-3</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="2">
+        <v>2023</v>
+      </c>
+      <c r="D4" s="2">
+        <v>11423484.0792</v>
+      </c>
+      <c r="E4" s="2">
+        <v>30582.725913679998</v>
+      </c>
+      <c r="F4" s="3">
+        <v>8.6595807302297054E-5</v>
+      </c>
+      <c r="G4" s="3">
+        <v>1.69804857508698E-3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" s="2">
+        <v>2024</v>
+      </c>
+      <c r="D5" s="2">
+        <v>11300772.48</v>
+      </c>
+      <c r="E5" s="2">
+        <v>31974.339456000002</v>
+      </c>
+      <c r="F5" s="3">
+        <v>5.7574468505698965E-4</v>
+      </c>
+      <c r="G5" s="3">
+        <v>6.8807976565944413E-4</v>
+      </c>
+      <c r="I5" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" s="2">
+        <v>2022</v>
+      </c>
+      <c r="D6" s="2">
+        <v>1821631.94</v>
+      </c>
+      <c r="E6" s="2">
+        <v>2075.48415338</v>
+      </c>
+      <c r="F6" s="3">
+        <v>2.1284775510358608E-2</v>
+      </c>
+      <c r="G6" s="3">
+        <v>9.5791533592884642E-4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" s="2">
+        <v>2021</v>
+      </c>
+      <c r="D7" s="2">
+        <v>1743254.7426</v>
+      </c>
+      <c r="E7" s="2">
+        <v>5649.2667995399997</v>
+      </c>
+      <c r="F7" s="3">
+        <v>4.3069526144492228E-2</v>
+      </c>
+      <c r="G7" s="3">
+        <v>2.415866866318173E-3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" s="2">
+        <v>2021</v>
+      </c>
+      <c r="D8" s="2">
+        <v>1730400.6762000001</v>
+      </c>
+      <c r="E8" s="2">
+        <v>11453.66344206</v>
+      </c>
+      <c r="F8" s="3">
+        <v>3.6351540108211508E-4</v>
+      </c>
+      <c r="G8" s="3">
+        <v>1.736681726385915E-4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" s="2">
+        <v>2022</v>
+      </c>
+      <c r="D9" s="2">
+        <v>1665422.6664</v>
+      </c>
+      <c r="E9" s="2">
+        <v>8756.6848730599995</v>
+      </c>
+      <c r="F9" s="3">
+        <v>7.9418686213037007E-3</v>
+      </c>
+      <c r="G9" s="3">
+        <v>6.2767209962179716E-4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10" s="2">
+        <v>2021</v>
+      </c>
+      <c r="D10" s="2">
+        <v>1647555.588</v>
+      </c>
+      <c r="E10" s="2">
+        <v>2286.3627977400001</v>
+      </c>
+      <c r="F10" s="3">
+        <v>3.8549628469778359E-3</v>
+      </c>
+      <c r="G10" s="3">
+        <v>4.9060229684840982E-4</v>
+      </c>
+      <c r="H10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C11" s="2">
+        <v>2023</v>
+      </c>
+      <c r="D11" s="2">
+        <v>1646977.0623999999</v>
+      </c>
+      <c r="E11" s="2">
+        <v>8501.7368701600008</v>
+      </c>
+      <c r="F11" s="3">
+        <v>3.13244725480416E-3</v>
+      </c>
+      <c r="G11" s="3">
+        <v>3.3557754651448161E-4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C12" s="2">
+        <v>2024</v>
+      </c>
+      <c r="D12" s="2">
+        <v>1581936.48</v>
+      </c>
+      <c r="E12" s="2">
+        <v>7766.5038239999994</v>
+      </c>
+      <c r="F12" s="3">
+        <v>1.717868258658569E-2</v>
+      </c>
+      <c r="G12" s="3">
+        <v>1.213271790439538E-4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C13" s="2">
+        <v>2023</v>
+      </c>
+      <c r="D13" s="2">
+        <v>1196714.5288</v>
+      </c>
+      <c r="E13" s="2">
+        <v>5296.7583626400001</v>
+      </c>
+      <c r="F13" s="3">
+        <v>0.1023070329623097</v>
+      </c>
+      <c r="G13" s="3">
+        <v>6.5499992306063972E-4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C14" s="2">
+        <v>2024</v>
+      </c>
+      <c r="D14" s="2">
+        <v>1186586.3999999999</v>
+      </c>
+      <c r="E14" s="2">
+        <v>4305.8265600000004</v>
+      </c>
+      <c r="F14" s="3">
+        <v>7.4943726483957598E-2</v>
+      </c>
+      <c r="G14" s="3">
+        <v>1.251650972211942E-3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C15" s="2">
+        <v>2022</v>
+      </c>
+      <c r="D15" s="2">
+        <v>1110225.9291999999</v>
+      </c>
+      <c r="E15" s="2">
+        <v>5731.3955529599998</v>
+      </c>
+      <c r="F15" s="3">
+        <v>2.961302102283718E-2</v>
+      </c>
+      <c r="G15" s="3">
+        <v>1.1157895805494109E-3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C16" s="2">
+        <v>2021</v>
+      </c>
+      <c r="D16" s="2">
+        <v>556393.38299999991</v>
+      </c>
+      <c r="E16" s="2">
+        <v>9537.5395684800005</v>
+      </c>
+      <c r="F16" s="3">
+        <v>2.2354784320331711E-5</v>
+      </c>
+      <c r="G16" s="3">
+        <v>0.66983975665100759</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C17" s="2">
+        <v>2024</v>
+      </c>
+      <c r="D17" s="2">
+        <v>438367.2</v>
+      </c>
+      <c r="E17" s="2">
+        <v>4244.5644000000002</v>
+      </c>
+      <c r="F17" s="3">
+        <v>1.0462699069897489E-4</v>
+      </c>
+      <c r="G17" s="3">
+        <v>1.199840435923177E-4</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C19" t="s">
+        <v>17</v>
+      </c>
+      <c r="D19">
+        <f>MEDIAN(D2:D17)</f>
+        <v>1656489.1272</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D21" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C22" t="s">
+        <v>18</v>
+      </c>
+      <c r="D22" s="2">
+        <f>AVERAGE(D11:D17)</f>
+        <v>1102457.2833428574</v>
+      </c>
+      <c r="E22" s="2">
+        <f t="shared" ref="E22:G22" si="0">AVERAGE(E11:E17)</f>
+        <v>6483.4750197485719</v>
+      </c>
+      <c r="F22" s="3">
+        <f t="shared" si="0"/>
+        <v>3.2471698869359092E-2</v>
+      </c>
+      <c r="G22" s="3">
+        <f t="shared" si="0"/>
+        <v>9.6205583699425765E-2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C23" t="s">
+        <v>19</v>
+      </c>
+      <c r="D23" s="2">
+        <f>AVERAGE(D2:D9)</f>
+        <v>6842663.1532999994</v>
+      </c>
+      <c r="E23" s="2">
+        <f t="shared" ref="E23:G23" si="1">AVERAGE(E2:E9)</f>
+        <v>19097.911644105003</v>
+      </c>
+      <c r="F23" s="3">
+        <f t="shared" si="1"/>
+        <v>1.286937987541362E-2</v>
+      </c>
+      <c r="G23" s="3">
+        <f t="shared" si="1"/>
+        <v>1.0604112949224313E-3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C25" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A26" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C26" s="2">
+        <v>2</v>
+      </c>
+      <c r="D26" s="6">
+        <v>12596210.486</v>
+      </c>
+      <c r="E26" s="6">
+        <v>29618.176784399999</v>
+      </c>
+      <c r="F26" s="3">
+        <v>1.244197192428451E-3</v>
+      </c>
+      <c r="G26" s="3">
+        <v>9.1204876912707078E-4</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A27" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C27" s="2">
+        <v>1</v>
+      </c>
+      <c r="D27" s="6">
+        <v>12460128.155999999</v>
+      </c>
+      <c r="E27" s="6">
+        <v>32672.95173072</v>
+      </c>
+      <c r="F27" s="3">
+        <v>2.8388815641284579E-2</v>
+      </c>
+      <c r="G27" s="3">
+        <v>1.009990774998547E-3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A28" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C28" s="2">
+        <v>3</v>
+      </c>
+      <c r="D28" s="6">
+        <v>11423484.0792</v>
+      </c>
+      <c r="E28" s="6">
+        <v>30582.725913679998</v>
+      </c>
+      <c r="F28" s="3">
+        <v>8.6595807302297054E-5</v>
+      </c>
+      <c r="G28" s="3">
+        <v>1.69804857508698E-3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A29" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C29" s="2">
+        <v>4</v>
+      </c>
+      <c r="D29" s="6">
+        <v>11300772.48</v>
+      </c>
+      <c r="E29" s="6">
+        <v>31974.339456000002</v>
+      </c>
+      <c r="F29" s="3">
+        <v>5.7574468505698965E-4</v>
+      </c>
+      <c r="G29" s="3">
+        <v>6.8807976565944413E-4</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B31" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="D31" s="6">
+        <f>AVERAGE(D26:D27)</f>
+        <v>12528169.320999999</v>
+      </c>
+      <c r="E31" s="6">
+        <f t="shared" ref="E31:G31" si="2">AVERAGE(E26:E27)</f>
+        <v>31145.56425756</v>
+      </c>
+      <c r="F31" s="3">
+        <f t="shared" si="2"/>
+        <v>1.4816506416856515E-2</v>
+      </c>
+      <c r="G31" s="3">
+        <f t="shared" si="2"/>
+        <v>9.6101977206280889E-4</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B32" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="D32" s="6">
+        <f>AVERAGE(D28:D29)</f>
+        <v>11362128.2796</v>
+      </c>
+      <c r="E32" s="6">
+        <f t="shared" ref="E32:G32" si="3">AVERAGE(E28:E29)</f>
+        <v>31278.53268484</v>
+      </c>
+      <c r="F32" s="3">
+        <f t="shared" si="3"/>
+        <v>3.3117024617964334E-4</v>
+      </c>
+      <c r="G32" s="3">
+        <f t="shared" si="3"/>
+        <v>1.193064170373212E-3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B34" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D34" s="6">
+        <f>D31/D32</f>
+        <v>1.1026252311808127</v>
+      </c>
+      <c r="E34" s="6">
+        <f t="shared" ref="E34:G34" si="4">E31/E32</f>
+        <v>0.99574889178403025</v>
+      </c>
+      <c r="F34" s="6">
+        <f t="shared" si="4"/>
+        <v>44.739847820807242</v>
+      </c>
+      <c r="G34" s="6">
+        <f t="shared" si="4"/>
+        <v>0.8055055175801521</v>
+      </c>
+      <c r="J34" s="8"/>
+      <c r="K34" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="L34" s="8" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="35" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="J35" s="8">
+        <v>6</v>
+      </c>
+      <c r="K35" s="9">
+        <v>0.3925398627504042</v>
+      </c>
+      <c r="L35" s="9">
+        <v>0.70595055998441802</v>
+      </c>
+    </row>
+    <row r="36" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="C36" s="2">
+        <f>MAX(C26:C29)</f>
+        <v>4</v>
+      </c>
+      <c r="D36" s="2">
+        <f t="shared" ref="D36:G36" si="5">MAX(D26:D29)</f>
+        <v>12596210.486</v>
+      </c>
+      <c r="E36" s="2">
+        <f t="shared" si="5"/>
+        <v>32672.95173072</v>
+      </c>
+      <c r="F36" s="2">
+        <f t="shared" si="5"/>
+        <v>2.8388815641284579E-2</v>
+      </c>
+      <c r="G36" s="2">
+        <f t="shared" si="5"/>
+        <v>1.69804857508698E-3</v>
+      </c>
+      <c r="J36" s="8">
+        <v>7</v>
+      </c>
+      <c r="K36" s="6">
+        <v>0.66617557589878618</v>
+      </c>
+      <c r="L36" s="6">
+        <v>0.57703403741966097</v>
+      </c>
+    </row>
+    <row r="37" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="C37" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F37" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G37" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="J37" s="8">
+        <v>9</v>
+      </c>
+      <c r="K37" s="6">
+        <v>0.17309364530987559</v>
+      </c>
+      <c r="L37" s="6">
+        <v>0.87137739656061919</v>
+      </c>
+    </row>
+    <row r="38" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="C38" s="2">
+        <f>C26/C$36</f>
+        <v>0.5</v>
+      </c>
+      <c r="D38" s="2">
+        <f t="shared" ref="D38:G38" si="6">D26/D$36</f>
+        <v>1</v>
+      </c>
+      <c r="E38" s="2">
+        <f t="shared" si="6"/>
+        <v>0.9065044697676391</v>
+      </c>
+      <c r="F38" s="2">
+        <f t="shared" si="6"/>
+        <v>4.3827020054301634E-2</v>
+      </c>
+      <c r="G38" s="2">
+        <f t="shared" si="6"/>
+        <v>0.53711582961067672</v>
+      </c>
+    </row>
+    <row r="39" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="C39" s="2">
+        <f t="shared" ref="C39:G41" si="7">C27/C$36</f>
+        <v>0.25</v>
+      </c>
+      <c r="D39" s="2">
+        <f t="shared" si="7"/>
+        <v>0.98919656589168237</v>
+      </c>
+      <c r="E39" s="2">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+      <c r="F39" s="2">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+      <c r="G39" s="2">
+        <f t="shared" si="7"/>
+        <v>0.5947949839696498</v>
+      </c>
+      <c r="J39" t="s">
+        <v>30</v>
+      </c>
+      <c r="K39" s="6">
+        <f>AVERAGE(K35:K37)</f>
+        <v>0.41060302798635534</v>
+      </c>
+      <c r="L39" s="6">
+        <f>AVERAGE(L35:L37)</f>
+        <v>0.71812066465489943</v>
+      </c>
+    </row>
+    <row r="40" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="C40" s="2">
+        <f t="shared" si="7"/>
+        <v>0.75</v>
+      </c>
+      <c r="D40" s="2">
+        <f t="shared" si="7"/>
+        <v>0.90689847489422148</v>
+      </c>
+      <c r="E40" s="2">
+        <f t="shared" si="7"/>
+        <v>0.93602580402692193</v>
+      </c>
+      <c r="F40" s="2">
+        <f t="shared" si="7"/>
+        <v>3.0503494191693107E-3</v>
+      </c>
+      <c r="G40" s="2">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="C41" s="2">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+      <c r="D41" s="2">
+        <f t="shared" si="7"/>
+        <v>0.89715652914503075</v>
+      </c>
+      <c r="E41" s="2">
+        <f t="shared" si="7"/>
+        <v>0.97861802384805219</v>
+      </c>
+      <c r="F41" s="2">
+        <f t="shared" si="7"/>
+        <v>2.0280687025904316E-2</v>
+      </c>
+      <c r="G41" s="2">
+        <f t="shared" si="7"/>
+        <v>0.40521795180340958</v>
+      </c>
+    </row>
+    <row r="43" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="C43" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="D43" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="E43" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="F43" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="G43" s="8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="44" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="C44" s="6">
+        <v>0.89715652914503075</v>
+      </c>
+      <c r="D44" s="2">
+        <v>1</v>
+      </c>
+      <c r="E44" s="2">
+        <v>0.97861802384805219</v>
+      </c>
+      <c r="F44" s="2">
+        <v>2.0280687025904316E-2</v>
+      </c>
+      <c r="G44" s="2">
+        <v>0.40521795180340958</v>
+      </c>
+    </row>
+    <row r="45" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="C45" s="6">
+        <v>0.90689847489422148</v>
+      </c>
+      <c r="D45" s="2">
+        <v>0.75</v>
+      </c>
+      <c r="E45" s="2">
+        <v>0.93602580402692193</v>
+      </c>
+      <c r="F45" s="2">
+        <v>3.0503494191693107E-3</v>
+      </c>
+      <c r="G45" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="C46" s="6">
+        <v>0.98919656589168237</v>
+      </c>
+      <c r="D46" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="E46" s="2">
+        <v>1</v>
+      </c>
+      <c r="F46" s="2">
+        <v>1</v>
+      </c>
+      <c r="G46" s="2">
+        <v>0.5947949839696498</v>
+      </c>
+    </row>
+    <row r="47" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="C47" s="6">
+        <v>1</v>
+      </c>
+      <c r="D47" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="E47" s="2">
+        <v>0.9065044697676391</v>
+      </c>
+      <c r="F47" s="2">
+        <v>4.3827020054301634E-2</v>
+      </c>
+      <c r="G47" s="2">
+        <v>0.53711582961067672</v>
+      </c>
+    </row>
+    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A50" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C50" s="2">
+        <v>1</v>
+      </c>
+      <c r="D50" s="6">
+        <v>1743254.7426</v>
+      </c>
+      <c r="E50" s="6">
+        <v>5649.2667995399997</v>
+      </c>
+      <c r="F50" s="3">
+        <v>4.3069526144492228E-2</v>
+      </c>
+      <c r="G50" s="3">
+        <v>2.415866866318173E-3</v>
+      </c>
+    </row>
+    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A51" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C51" s="2">
+        <v>3</v>
+      </c>
+      <c r="D51" s="6">
+        <v>1196714.5288</v>
+      </c>
+      <c r="E51" s="6">
+        <v>5296.7583626400001</v>
+      </c>
+      <c r="F51" s="3">
+        <v>0.1023070329623097</v>
+      </c>
+      <c r="G51" s="3">
+        <v>6.5499992306063972E-4</v>
+      </c>
+    </row>
+    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A52" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C52" s="2">
+        <v>4</v>
+      </c>
+      <c r="D52" s="6">
+        <v>1186586.3999999999</v>
+      </c>
+      <c r="E52" s="6">
+        <v>4305.8265600000004</v>
+      </c>
+      <c r="F52" s="3">
+        <v>7.4943726483957598E-2</v>
+      </c>
+      <c r="G52" s="3">
+        <v>1.251650972211942E-3</v>
+      </c>
+    </row>
+    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A53" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C53" s="2">
+        <v>2</v>
+      </c>
+      <c r="D53" s="6">
+        <v>1110225.9291999999</v>
+      </c>
+      <c r="E53" s="6">
+        <v>5731.3955529599998</v>
+      </c>
+      <c r="F53" s="3">
+        <v>2.961302102283718E-2</v>
+      </c>
+      <c r="G53" s="3">
+        <v>1.1157895805494109E-3</v>
+      </c>
+    </row>
+    <row r="55" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B55" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="D55" s="6">
+        <f>AVERAGE(D50:D51)</f>
+        <v>1469984.6357</v>
+      </c>
+      <c r="E55" s="6">
+        <f t="shared" ref="E55:G55" si="8">AVERAGE(E50:E51)</f>
+        <v>5473.0125810899999</v>
+      </c>
+      <c r="F55" s="3">
+        <f t="shared" si="8"/>
+        <v>7.2688279553400958E-2</v>
+      </c>
+      <c r="G55" s="3">
+        <f t="shared" si="8"/>
+        <v>1.5354333946894063E-3</v>
+      </c>
+    </row>
+    <row r="56" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B56" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="D56" s="6">
+        <f>AVERAGE(D52:D53)</f>
+        <v>1148406.1645999998</v>
+      </c>
+      <c r="E56" s="6">
+        <f t="shared" ref="E56:G56" si="9">AVERAGE(E52:E53)</f>
+        <v>5018.6110564800001</v>
+      </c>
+      <c r="F56" s="3">
+        <f t="shared" si="9"/>
+        <v>5.2278373753397389E-2</v>
+      </c>
+      <c r="G56" s="3">
+        <f t="shared" si="9"/>
+        <v>1.1837202763806765E-3</v>
+      </c>
+    </row>
+    <row r="58" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B58" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D58" s="6">
+        <f>D55/D56</f>
+        <v>1.2800215472650383</v>
+      </c>
+      <c r="E58" s="6">
+        <f t="shared" ref="E58:G58" si="10">E55/E56</f>
+        <v>1.090543283688677</v>
+      </c>
+      <c r="F58" s="6">
+        <f t="shared" si="10"/>
+        <v>1.3904082000767517</v>
+      </c>
+      <c r="G58" s="6">
+        <f t="shared" si="10"/>
+        <v>1.297125195307224</v>
+      </c>
+    </row>
+    <row r="60" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C60" s="2">
+        <f>MAX(C50:C53)</f>
+        <v>4</v>
+      </c>
+      <c r="D60" s="2">
+        <f t="shared" ref="D60:G60" si="11">MAX(D50:D53)</f>
+        <v>1743254.7426</v>
+      </c>
+      <c r="E60" s="2">
+        <f t="shared" si="11"/>
+        <v>5731.3955529599998</v>
+      </c>
+      <c r="F60" s="2">
+        <f t="shared" si="11"/>
+        <v>0.1023070329623097</v>
+      </c>
+      <c r="G60" s="2">
+        <f t="shared" si="11"/>
+        <v>2.415866866318173E-3</v>
+      </c>
+    </row>
+    <row r="61" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C61" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="D61" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E61" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F61" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G61" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="J61" s="2"/>
+      <c r="K61" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="L61" s="8" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="62" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C62" s="2">
+        <f>C50/C$60</f>
+        <v>0.25</v>
+      </c>
+      <c r="D62" s="2">
+        <f t="shared" ref="D62:G62" si="12">D50/D$60</f>
+        <v>1</v>
+      </c>
+      <c r="E62" s="2">
+        <f t="shared" si="12"/>
+        <v>0.98567037422891113</v>
+      </c>
+      <c r="F62" s="2">
+        <f t="shared" si="12"/>
+        <v>0.42098304385739743</v>
+      </c>
+      <c r="G62" s="2">
+        <f t="shared" si="12"/>
+        <v>1</v>
+      </c>
+      <c r="J62" s="8">
+        <v>6</v>
+      </c>
+      <c r="K62" s="6">
+        <f>0.5*(D47*E47+E47*F47+F47*G47+G47*D47)</f>
+        <v>0.3925398627504042</v>
+      </c>
+      <c r="L62" s="6">
+        <f>0.5*(D44*E44+E44*F44+F44*G44+G44*D44)</f>
+        <v>0.70595055998441802</v>
+      </c>
+    </row>
+    <row r="63" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C63" s="2">
+        <f t="shared" ref="C63:G65" si="13">C51/C$60</f>
+        <v>0.75</v>
+      </c>
+      <c r="D63" s="2">
+        <f t="shared" si="13"/>
+        <v>0.68648287571278566</v>
+      </c>
+      <c r="E63" s="2">
+        <f t="shared" si="13"/>
+        <v>0.92416555683449042</v>
+      </c>
+      <c r="F63" s="2">
+        <f t="shared" si="13"/>
+        <v>1</v>
+      </c>
+      <c r="G63" s="2">
+        <f t="shared" si="13"/>
+        <v>0.27112417997555965</v>
+      </c>
+    </row>
+    <row r="64" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C64" s="2">
+        <f t="shared" si="13"/>
+        <v>1</v>
+      </c>
+      <c r="D64" s="2">
+        <f t="shared" si="13"/>
+        <v>0.6806729796875528</v>
+      </c>
+      <c r="E64" s="2">
+        <f t="shared" si="13"/>
+        <v>0.75127017847795219</v>
+      </c>
+      <c r="F64" s="2">
+        <f t="shared" si="13"/>
+        <v>0.73253738588594541</v>
+      </c>
+      <c r="G64" s="2">
+        <f t="shared" si="13"/>
+        <v>0.51809600506648856</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C65" s="2">
+        <f t="shared" si="13"/>
+        <v>0.5</v>
+      </c>
+      <c r="D65" s="2">
+        <f t="shared" si="13"/>
+        <v>0.63686958771392121</v>
+      </c>
+      <c r="E65" s="2">
+        <f t="shared" si="13"/>
+        <v>1</v>
+      </c>
+      <c r="F65" s="2">
+        <f t="shared" si="13"/>
+        <v>0.28945244686889443</v>
+      </c>
+      <c r="G65" s="2">
+        <f t="shared" si="13"/>
+        <v>0.46185888639215267</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C67" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="D67" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="E67" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="F67" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="G67" s="8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C68" s="6">
+        <v>0.63686958771392121</v>
+      </c>
+      <c r="D68" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="E68" s="2">
+        <v>1</v>
+      </c>
+      <c r="F68" s="2">
+        <v>0.28945244686889443</v>
+      </c>
+      <c r="G68" s="2">
+        <v>0.46185888639215267</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C69" s="6">
+        <v>0.6806729796875528</v>
+      </c>
+      <c r="D69" s="2">
+        <v>1</v>
+      </c>
+      <c r="E69" s="2">
+        <v>0.75127017847795219</v>
+      </c>
+      <c r="F69" s="2">
+        <v>0.73253738588594541</v>
+      </c>
+      <c r="G69" s="2">
+        <v>0.51809600506648856</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C70" s="6">
+        <v>0.68648287571278566</v>
+      </c>
+      <c r="D70" s="2">
+        <v>0.75</v>
+      </c>
+      <c r="E70" s="2">
+        <v>0.92416555683449042</v>
+      </c>
+      <c r="F70" s="2">
+        <v>1</v>
+      </c>
+      <c r="G70" s="2">
+        <v>0.27112417997555965</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C71" s="6">
+        <v>1</v>
+      </c>
+      <c r="D71" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="E71" s="2">
+        <v>0.98567037422891113</v>
+      </c>
+      <c r="F71" s="2">
+        <v>0.42098304385739743</v>
+      </c>
+      <c r="G71" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A74" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C74" s="2">
+        <v>1</v>
+      </c>
+      <c r="D74" s="6">
+        <v>1730400.6762000001</v>
+      </c>
+      <c r="E74" s="6">
+        <v>11453.66344206</v>
+      </c>
+      <c r="F74" s="3">
+        <v>3.6351540108211508E-4</v>
+      </c>
+      <c r="G74" s="3">
+        <v>1.736681726385915E-4</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A75" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C75" s="2">
+        <v>2</v>
+      </c>
+      <c r="D75" s="6">
+        <v>1665422.6664</v>
+      </c>
+      <c r="E75" s="6">
+        <v>8756.6848730599995</v>
+      </c>
+      <c r="F75" s="3">
+        <v>7.9418686213037007E-3</v>
+      </c>
+      <c r="G75" s="3">
+        <v>6.2767209962179716E-4</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A76" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C76" s="2">
+        <v>3</v>
+      </c>
+      <c r="D76" s="6">
+        <v>1646977.0623999999</v>
+      </c>
+      <c r="E76" s="6">
+        <v>8501.7368701600008</v>
+      </c>
+      <c r="F76" s="3">
+        <v>3.13244725480416E-3</v>
+      </c>
+      <c r="G76" s="3">
+        <v>3.3557754651448161E-4</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A77" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B77" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C77" s="2">
+        <v>4</v>
+      </c>
+      <c r="D77" s="6">
+        <v>1581936.48</v>
+      </c>
+      <c r="E77" s="6">
+        <v>7766.5038239999994</v>
+      </c>
+      <c r="F77" s="3">
+        <v>1.717868258658569E-2</v>
+      </c>
+      <c r="G77" s="3">
+        <v>1.213271790439538E-4</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B79" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="D79" s="6">
+        <f>AVERAGE(D74:D75)</f>
+        <v>1697911.6713</v>
+      </c>
+      <c r="E79" s="6">
+        <f t="shared" ref="E79:G79" si="14">AVERAGE(E74:E75)</f>
+        <v>10105.174157559999</v>
+      </c>
+      <c r="F79" s="3">
+        <f t="shared" si="14"/>
+        <v>4.1526920111929081E-3</v>
+      </c>
+      <c r="G79" s="3">
+        <f t="shared" si="14"/>
+        <v>4.0067013613019435E-4</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B80" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="D80" s="6">
+        <f>AVERAGE(D76:D77)</f>
+        <v>1614456.7711999998</v>
+      </c>
+      <c r="E80" s="6">
+        <f t="shared" ref="E80:G80" si="15">AVERAGE(E76:E77)</f>
+        <v>8134.1203470800001</v>
+      </c>
+      <c r="F80" s="3">
+        <f t="shared" si="15"/>
+        <v>1.0155564920694925E-2</v>
+      </c>
+      <c r="G80" s="3">
+        <f t="shared" si="15"/>
+        <v>2.2845236277921772E-4</v>
+      </c>
+    </row>
+    <row r="82" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B82" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D82" s="6">
+        <f>D79/D80</f>
+        <v>1.0516922481844897</v>
+      </c>
+      <c r="E82" s="6">
+        <f t="shared" ref="E82:G82" si="16">E79/E80</f>
+        <v>1.2423192338416251</v>
+      </c>
+      <c r="F82" s="6">
+        <f t="shared" si="16"/>
+        <v>0.40890802664562625</v>
+      </c>
+      <c r="G82" s="6">
+        <f t="shared" si="16"/>
+        <v>1.7538454461835107</v>
+      </c>
+    </row>
+    <row r="84" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="C84" s="2">
+        <f>MAX(C74:C77)</f>
+        <v>4</v>
+      </c>
+      <c r="D84" s="2">
+        <f t="shared" ref="D84:G84" si="17">MAX(D74:D77)</f>
+        <v>1730400.6762000001</v>
+      </c>
+      <c r="E84" s="2">
+        <f t="shared" si="17"/>
+        <v>11453.66344206</v>
+      </c>
+      <c r="F84" s="2">
+        <f t="shared" si="17"/>
+        <v>1.717868258658569E-2</v>
+      </c>
+      <c r="G84" s="2">
+        <f t="shared" si="17"/>
+        <v>6.2767209962179716E-4</v>
+      </c>
+      <c r="J84" s="2"/>
+      <c r="K84" s="8"/>
+      <c r="L84" s="8"/>
+    </row>
+    <row r="85" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="C85" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="D85" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E85" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F85" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G85" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="J85" s="2"/>
+      <c r="K85" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="L85" s="8" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="86" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="C86" s="2">
+        <f t="shared" ref="C86:G89" si="18">C74/C$84</f>
+        <v>0.25</v>
+      </c>
+      <c r="D86" s="2">
+        <f t="shared" si="18"/>
+        <v>1</v>
+      </c>
+      <c r="E86" s="2">
+        <f t="shared" si="18"/>
+        <v>1</v>
+      </c>
+      <c r="F86" s="2">
+        <f t="shared" si="18"/>
+        <v>2.1160842762527853E-2</v>
+      </c>
+      <c r="G86" s="2">
+        <f t="shared" si="18"/>
+        <v>0.2766861435186222</v>
+      </c>
+      <c r="J86" s="8">
+        <v>7</v>
+      </c>
+      <c r="K86" s="6">
+        <f>0.5*(D71*E71+E71*F71+F71*G71+G71*D71)</f>
+        <v>0.66617557589878618</v>
+      </c>
+      <c r="L86" s="6">
+        <f>0.5*(D68*E68+E68*F68+F68*G68+G68*D68)</f>
+        <v>0.57703403741966097</v>
+      </c>
+    </row>
+    <row r="87" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="C87" s="2">
+        <f t="shared" si="18"/>
+        <v>0.5</v>
+      </c>
+      <c r="D87" s="2">
+        <f t="shared" si="18"/>
+        <v>0.96244915371699158</v>
+      </c>
+      <c r="E87" s="2">
+        <f t="shared" si="18"/>
+        <v>0.76453135866589295</v>
+      </c>
+      <c r="F87" s="2">
+        <f t="shared" si="18"/>
+        <v>0.46230952701258149</v>
+      </c>
+      <c r="G87" s="2">
+        <f t="shared" si="18"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="C88" s="2">
+        <f t="shared" si="18"/>
+        <v>0.75</v>
+      </c>
+      <c r="D88" s="2">
+        <f t="shared" si="18"/>
+        <v>0.95178942371705477</v>
+      </c>
+      <c r="E88" s="2">
+        <f t="shared" si="18"/>
+        <v>0.74227227935998441</v>
+      </c>
+      <c r="F88" s="2">
+        <f t="shared" si="18"/>
+        <v>0.18234502203621789</v>
+      </c>
+      <c r="G88" s="2">
+        <f t="shared" si="18"/>
+        <v>0.53463830352931618</v>
+      </c>
+    </row>
+    <row r="89" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="C89" s="2">
+        <f t="shared" si="18"/>
+        <v>1</v>
+      </c>
+      <c r="D89" s="2">
+        <f t="shared" si="18"/>
+        <v>0.91420241667610136</v>
+      </c>
+      <c r="E89" s="2">
+        <f t="shared" si="18"/>
+        <v>0.67808032454314493</v>
+      </c>
+      <c r="F89" s="2">
+        <f t="shared" si="18"/>
+        <v>1</v>
+      </c>
+      <c r="G89" s="2">
+        <f t="shared" si="18"/>
+        <v>0.19329707201747426</v>
+      </c>
+    </row>
+    <row r="91" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="C91" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="D91" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="E91" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="F91" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="G91" s="8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="92" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="C92" s="6">
+        <v>0.91420241667610136</v>
+      </c>
+      <c r="D92" s="2">
+        <v>1</v>
+      </c>
+      <c r="E92" s="2">
+        <v>0.67808032454314493</v>
+      </c>
+      <c r="F92" s="2">
+        <v>1</v>
+      </c>
+      <c r="G92" s="2">
+        <v>0.19329707201747426</v>
+      </c>
+    </row>
+    <row r="93" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="C93" s="6">
+        <v>0.95178942371705477</v>
+      </c>
+      <c r="D93" s="2">
+        <v>0.75</v>
+      </c>
+      <c r="E93" s="2">
+        <v>0.74227227935998441</v>
+      </c>
+      <c r="F93" s="2">
+        <v>0.18234502203621789</v>
+      </c>
+      <c r="G93" s="2">
+        <v>0.53463830352931618</v>
+      </c>
+    </row>
+    <row r="94" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="C94" s="6">
+        <v>0.96244915371699158</v>
+      </c>
+      <c r="D94" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="E94" s="2">
+        <v>0.76453135866589295</v>
+      </c>
+      <c r="F94" s="2">
+        <v>0.46230952701258149</v>
+      </c>
+      <c r="G94" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="95" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="C95" s="6">
+        <v>1</v>
+      </c>
+      <c r="D95" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="E95" s="2">
+        <v>1</v>
+      </c>
+      <c r="F95" s="2">
+        <v>2.1160842762527853E-2</v>
+      </c>
+      <c r="G95" s="2">
+        <v>0.2766861435186222</v>
+      </c>
+    </row>
+    <row r="103" spans="10:12" x14ac:dyDescent="0.25">
+      <c r="J103" s="2"/>
+      <c r="K103" s="8"/>
+      <c r="L103" s="8"/>
+    </row>
+    <row r="104" spans="10:12" x14ac:dyDescent="0.25">
+      <c r="J104" s="8"/>
+      <c r="K104" s="6"/>
+      <c r="L104" s="6"/>
+    </row>
+    <row r="106" spans="10:12" x14ac:dyDescent="0.25">
+      <c r="J106" s="2"/>
+      <c r="K106" s="8"/>
+      <c r="L106" s="8"/>
+    </row>
+    <row r="107" spans="10:12" x14ac:dyDescent="0.25">
+      <c r="J107" s="8"/>
+      <c r="K107" s="6"/>
+      <c r="L107" s="6"/>
+    </row>
+    <row r="109" spans="10:12" x14ac:dyDescent="0.25">
+      <c r="J109" s="2"/>
+      <c r="K109" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="L109" s="8" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="110" spans="10:12" x14ac:dyDescent="0.25">
+      <c r="J110" s="8">
+        <v>9</v>
+      </c>
+      <c r="K110" s="6">
+        <f>0.5*(D95*E95+E95*F95+F95*G95+G95*D95)</f>
+        <v>0.17309364530987559</v>
+      </c>
+      <c r="L110" s="6">
+        <f>0.5*(D92*E92+E92*F92+F92*G92+G92*D92)</f>
+        <v>0.87137739656061919</v>
+      </c>
+    </row>
+    <row r="113" spans="10:12" x14ac:dyDescent="0.25">
+      <c r="J113" s="2"/>
+      <c r="K113" s="8"/>
+      <c r="L113" s="8"/>
+    </row>
+    <row r="114" spans="10:12" x14ac:dyDescent="0.25">
+      <c r="J114" s="8"/>
+      <c r="K114" s="6"/>
+      <c r="L114" s="6"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="D2:D17">
+    <cfRule type="colorScale" priority="32">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E2:E17">
+    <cfRule type="colorScale" priority="31">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F2:F17">
+    <cfRule type="colorScale" priority="30">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G2:G17">
+    <cfRule type="colorScale" priority="29">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D22:D23">
+    <cfRule type="colorScale" priority="28">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E22:E23">
+    <cfRule type="colorScale" priority="27">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F22:F23">
+    <cfRule type="colorScale" priority="26">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G22:G23">
+    <cfRule type="colorScale" priority="25">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D26:D29">
+    <cfRule type="colorScale" priority="24">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E26:E29">
+    <cfRule type="colorScale" priority="23">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F26:F29">
+    <cfRule type="colorScale" priority="22">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G26:G29">
+    <cfRule type="colorScale" priority="21">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D31:D32">
+    <cfRule type="colorScale" priority="20">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E31:E32">
+    <cfRule type="colorScale" priority="19">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F31:F32">
+    <cfRule type="colorScale" priority="18">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G31:G32">
+    <cfRule type="colorScale" priority="17">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D50:D53">
+    <cfRule type="colorScale" priority="16">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E50:E53">
+    <cfRule type="colorScale" priority="15">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F50:F53">
+    <cfRule type="colorScale" priority="14">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G50:G53">
+    <cfRule type="colorScale" priority="13">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D55:D56">
+    <cfRule type="colorScale" priority="12">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E55:E56">
+    <cfRule type="colorScale" priority="11">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F55:F56">
+    <cfRule type="colorScale" priority="10">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G55:G56">
+    <cfRule type="colorScale" priority="9">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D74:D77">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E74:E77">
+    <cfRule type="colorScale" priority="7">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F74:F77">
+    <cfRule type="colorScale" priority="6">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G74:G77">
+    <cfRule type="colorScale" priority="5">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D79:D80">
+    <cfRule type="colorScale" priority="4">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E79:E80">
+    <cfRule type="colorScale" priority="3">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F79:F80">
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G79:G80">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
 </file>